--- a/research/traditional_assets/database/data/pakistan/pakistan_education.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_education.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1687157983897822</v>
+        <v>0.1682584725744519</v>
       </c>
       <c r="C2">
-        <v>1.136499753095292</v>
+        <v>1.129232389523557</v>
       </c>
       <c r="D2">
-        <v>1.082499753095292</v>
+        <v>1.086542389523557</v>
       </c>
       <c r="E2">
-        <v>-0.031</v>
+        <v>-0.01969</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.01131</v>
       </c>
       <c r="G2">
         <v>0.054</v>
@@ -1445,28 +1445,28 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.000568893</v>
       </c>
       <c r="N2">
-        <v>0.01866666666666666</v>
+        <v>0.01809777366666666</v>
       </c>
       <c r="O2">
-        <v>0.005413333333333332</v>
+        <v>0.005248354363333332</v>
       </c>
       <c r="P2">
-        <v>0.01325333333333333</v>
+        <v>0.01284941930333333</v>
       </c>
       <c r="Q2">
-        <v>0.01725333333333334</v>
+        <v>0.01684941930333334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1687157983897822</v>
+        <v>0.1695973157317696</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7571289721411459</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>32.81226288013153</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1682584725744519</v>
+        <v>0.1678011467591215</v>
       </c>
       <c r="C3">
-        <v>1.129232389523557</v>
+        <v>1.121995333896457</v>
       </c>
       <c r="D3">
-        <v>1.086542389523557</v>
+        <v>1.090615333896457</v>
       </c>
       <c r="E3">
-        <v>-0.01969</v>
+        <v>-0.008379999999999999</v>
       </c>
       <c r="F3">
-        <v>0.01131</v>
+        <v>0.02262</v>
       </c>
       <c r="G3">
         <v>0.054</v>
@@ -1527,28 +1527,28 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M3">
-        <v>0.000568893</v>
+        <v>0.001137786</v>
       </c>
       <c r="N3">
-        <v>0.01809777366666666</v>
+        <v>0.01752888066666666</v>
       </c>
       <c r="O3">
-        <v>0.005248354363333332</v>
+        <v>0.005083375393333332</v>
       </c>
       <c r="P3">
-        <v>0.01284941930333333</v>
+        <v>0.01244550527333333</v>
       </c>
       <c r="Q3">
-        <v>0.01684941930333334</v>
+        <v>0.01644550527333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1695973157317696</v>
+        <v>0.1704968232235934</v>
       </c>
       <c r="T3">
-        <v>0.7571289721411459</v>
+        <v>0.7626302479862008</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>32.81226288013153</v>
+        <v>16.40613144006576</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1678011467591215</v>
+        <v>0.1673757709437912</v>
       </c>
       <c r="C4">
-        <v>1.121995333896457</v>
+        <v>1.114501237207343</v>
       </c>
       <c r="D4">
-        <v>1.090615333896457</v>
+        <v>1.094431237207343</v>
       </c>
       <c r="E4">
-        <v>-0.008379999999999999</v>
+        <v>0.002930000000000002</v>
       </c>
       <c r="F4">
-        <v>0.02262</v>
+        <v>0.03393</v>
       </c>
       <c r="G4">
         <v>0.054</v>
@@ -1609,45 +1609,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M4">
-        <v>0.001137786</v>
+        <v>0.001757574</v>
       </c>
       <c r="N4">
-        <v>0.01752888066666666</v>
+        <v>0.01690909266666666</v>
       </c>
       <c r="O4">
-        <v>0.005083375393333332</v>
+        <v>0.004903636873333332</v>
       </c>
       <c r="P4">
-        <v>0.01244550527333333</v>
+        <v>0.01200545579333333</v>
       </c>
       <c r="Q4">
-        <v>0.01644550527333333</v>
+        <v>0.01600545579333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1704968232235934</v>
+        <v>0.1714148772616404</v>
       </c>
       <c r="T4">
-        <v>0.7626302479862008</v>
+        <v>0.7682449521991951</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.29</v>
       </c>
       <c r="W4">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>16.40613144006576</v>
+        <v>10.62070027587269</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1673757709437912</v>
+        <v>0.1669773751284608</v>
       </c>
       <c r="C5">
-        <v>1.114501237207343</v>
+        <v>1.106789407448348</v>
       </c>
       <c r="D5">
-        <v>1.094431237207343</v>
+        <v>1.098029407448348</v>
       </c>
       <c r="E5">
-        <v>0.002930000000000002</v>
+        <v>0.01424</v>
       </c>
       <c r="F5">
-        <v>0.03393</v>
+        <v>0.04524</v>
       </c>
       <c r="G5">
         <v>0.054</v>
@@ -1691,45 +1691,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M5">
-        <v>0.001757574</v>
+        <v>0.00242034</v>
       </c>
       <c r="N5">
-        <v>0.01690909266666666</v>
+        <v>0.01624632666666666</v>
       </c>
       <c r="O5">
-        <v>0.004903636873333332</v>
+        <v>0.004711434733333333</v>
       </c>
       <c r="P5">
-        <v>0.01200545579333333</v>
+        <v>0.01153489193333333</v>
       </c>
       <c r="Q5">
-        <v>0.01600545579333333</v>
+        <v>0.01553489193333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1714148772616404</v>
+        <v>0.17235205742548</v>
       </c>
       <c r="T5">
-        <v>0.7682449521991951</v>
+        <v>0.7739766294166265</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.29</v>
       </c>
       <c r="W5">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>10.62070027587269</v>
+        <v>7.712415060143065</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1669773751284608</v>
+        <v>0.1666066693131304</v>
       </c>
       <c r="C6">
-        <v>1.106789407448348</v>
+        <v>1.098848806580525</v>
       </c>
       <c r="D6">
-        <v>1.098029407448348</v>
+        <v>1.101398806580525</v>
       </c>
       <c r="E6">
-        <v>0.01424</v>
+        <v>0.02555</v>
       </c>
       <c r="F6">
-        <v>0.04524</v>
+        <v>0.05655</v>
       </c>
       <c r="G6">
         <v>0.054</v>
@@ -1773,45 +1773,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M6">
-        <v>0.00242034</v>
+        <v>0.003127215</v>
       </c>
       <c r="N6">
-        <v>0.01624632666666666</v>
+        <v>0.01553945166666666</v>
       </c>
       <c r="O6">
-        <v>0.004711434733333333</v>
+        <v>0.004506440983333332</v>
       </c>
       <c r="P6">
-        <v>0.01153489193333333</v>
+        <v>0.01103301068333333</v>
       </c>
       <c r="Q6">
-        <v>0.01553489193333333</v>
+        <v>0.01503301068333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.17235205742548</v>
+        <v>0.173308967698032</v>
       </c>
       <c r="T6">
-        <v>0.7739766294166265</v>
+        <v>0.779828973522846</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.29</v>
       </c>
       <c r="W6">
-        <v>0.037985</v>
+        <v>0.039263</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>7.712415060143065</v>
+        <v>5.969102433528446</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1666066693131304</v>
+        <v>0.1661848434978</v>
       </c>
       <c r="C7">
-        <v>1.098848806580525</v>
+        <v>1.09139808351349</v>
       </c>
       <c r="D7">
-        <v>1.101398806580525</v>
+        <v>1.10525808351349</v>
       </c>
       <c r="E7">
-        <v>0.02555</v>
+        <v>0.03686</v>
       </c>
       <c r="F7">
-        <v>0.05655</v>
+        <v>0.06786</v>
       </c>
       <c r="G7">
         <v>0.054</v>
@@ -1855,28 +1855,28 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M7">
-        <v>0.003127215</v>
+        <v>0.003752658</v>
       </c>
       <c r="N7">
-        <v>0.01553945166666666</v>
+        <v>0.01491400866666666</v>
       </c>
       <c r="O7">
-        <v>0.004506440983333332</v>
+        <v>0.004325062513333333</v>
       </c>
       <c r="P7">
-        <v>0.01103301068333333</v>
+        <v>0.01058894615333333</v>
       </c>
       <c r="Q7">
-        <v>0.01503301068333333</v>
+        <v>0.01458894615333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.173308967698032</v>
+        <v>0.174286237763617</v>
       </c>
       <c r="T7">
-        <v>0.779828973522846</v>
+        <v>0.7858058355887724</v>
       </c>
       <c r="U7">
         <v>0.0553</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>5.969102433528446</v>
+        <v>4.974252027940373</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1661848434978</v>
+        <v>0.1658872676824697</v>
       </c>
       <c r="C8">
-        <v>1.09139808351349</v>
+        <v>1.082826909050113</v>
       </c>
       <c r="D8">
-        <v>1.10525808351349</v>
+        <v>1.107996909050113</v>
       </c>
       <c r="E8">
-        <v>0.03686</v>
+        <v>0.04816999999999999</v>
       </c>
       <c r="F8">
-        <v>0.06786</v>
+        <v>0.07916999999999999</v>
       </c>
       <c r="G8">
         <v>0.054</v>
@@ -1937,45 +1937,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M8">
-        <v>0.003752658</v>
+        <v>0.004576026</v>
       </c>
       <c r="N8">
-        <v>0.01491400866666666</v>
+        <v>0.01409064066666666</v>
       </c>
       <c r="O8">
-        <v>0.004325062513333333</v>
+        <v>0.004086285793333332</v>
       </c>
       <c r="P8">
-        <v>0.01058894615333333</v>
+        <v>0.01000435487333333</v>
       </c>
       <c r="Q8">
-        <v>0.01458894615333333</v>
+        <v>0.01400435487333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.174286237763617</v>
+        <v>0.1752845243897523</v>
       </c>
       <c r="T8">
-        <v>0.7858058355887724</v>
+        <v>0.7919112323227833</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.29</v>
       </c>
       <c r="W8">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.974252027940373</v>
+        <v>4.079230901805774</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1658872676824697</v>
+        <v>0.1658410318671393</v>
       </c>
       <c r="C9">
-        <v>1.082826909050113</v>
+        <v>1.071943672629838</v>
       </c>
       <c r="D9">
-        <v>1.107996909050113</v>
+        <v>1.108423672629838</v>
       </c>
       <c r="E9">
-        <v>0.04817</v>
+        <v>0.05948000000000001</v>
       </c>
       <c r="F9">
-        <v>0.07917</v>
+        <v>0.09048</v>
       </c>
       <c r="G9">
         <v>0.054</v>
@@ -2019,45 +2019,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M9">
-        <v>0.004576026</v>
+        <v>0.005799768</v>
       </c>
       <c r="N9">
-        <v>0.01409064066666666</v>
+        <v>0.01286689866666666</v>
       </c>
       <c r="O9">
-        <v>0.004086285793333332</v>
+        <v>0.003731400613333333</v>
       </c>
       <c r="P9">
-        <v>0.01000435487333333</v>
+        <v>0.009135498053333331</v>
       </c>
       <c r="Q9">
-        <v>0.01400435487333333</v>
+        <v>0.01313549805333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1752845243897523</v>
+        <v>0.1763045128990645</v>
       </c>
       <c r="T9">
-        <v>0.7919112323227833</v>
+        <v>0.7981493550727508</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V9">
         <v>0.29</v>
       </c>
       <c r="W9">
-        <v>0.041038</v>
+        <v>0.045511</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.079230901805772</v>
+        <v>3.218519545379516</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1658410318671393</v>
+        <v>0.1659801060518089</v>
       </c>
       <c r="C10">
-        <v>1.071943672629838</v>
+        <v>1.059350988468509</v>
       </c>
       <c r="D10">
-        <v>1.108423672629838</v>
+        <v>1.107140988468509</v>
       </c>
       <c r="E10">
-        <v>0.05948000000000001</v>
+        <v>0.07078999999999999</v>
       </c>
       <c r="F10">
-        <v>0.09048</v>
+        <v>0.10179</v>
       </c>
       <c r="G10">
         <v>0.054</v>
@@ -2101,45 +2101,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M10">
-        <v>0.005799768</v>
+        <v>0.007318701</v>
       </c>
       <c r="N10">
-        <v>0.01286689866666666</v>
+        <v>0.01134796566666666</v>
       </c>
       <c r="O10">
-        <v>0.003731400613333333</v>
+        <v>0.003290910043333332</v>
       </c>
       <c r="P10">
-        <v>0.009135498053333331</v>
+        <v>0.008057055623333332</v>
       </c>
       <c r="Q10">
-        <v>0.01313549805333333</v>
+        <v>0.01205705562333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1763045128990645</v>
+        <v>0.1773469187382516</v>
       </c>
       <c r="T10">
-        <v>0.7981493550727508</v>
+        <v>0.8045245794216187</v>
       </c>
       <c r="U10">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V10">
         <v>0.29</v>
       </c>
       <c r="W10">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.218519545379516</v>
+        <v>2.550543691656028</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1659801060518089</v>
+        <v>0.1659530402364786</v>
       </c>
       <c r="C11">
-        <v>1.059350988468509</v>
+        <v>1.048290384351289</v>
       </c>
       <c r="D11">
-        <v>1.107140988468509</v>
+        <v>1.107390384351289</v>
       </c>
       <c r="E11">
-        <v>0.07078999999999999</v>
+        <v>0.08209999999999999</v>
       </c>
       <c r="F11">
-        <v>0.10179</v>
+        <v>0.1131</v>
       </c>
       <c r="G11">
         <v>0.054</v>
@@ -2183,45 +2183,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M11">
-        <v>0.007318701</v>
+        <v>0.008572980000000001</v>
       </c>
       <c r="N11">
-        <v>0.01134796566666666</v>
+        <v>0.01009368666666666</v>
       </c>
       <c r="O11">
-        <v>0.003290910043333332</v>
+        <v>0.002927169133333333</v>
       </c>
       <c r="P11">
-        <v>0.008057055623333332</v>
+        <v>0.007166517533333331</v>
       </c>
       <c r="Q11">
-        <v>0.01205705562333333</v>
+        <v>0.01116651753333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1773469187382516</v>
+        <v>0.1784124891516428</v>
       </c>
       <c r="T11">
-        <v>0.8045245794216187</v>
+        <v>0.8110414754226837</v>
       </c>
       <c r="U11">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.29</v>
       </c>
       <c r="W11">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.550543691656028</v>
+        <v>2.177383671333266</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1659530402364786</v>
+        <v>0.1667857844211482</v>
       </c>
       <c r="C12">
-        <v>1.048290384351289</v>
+        <v>1.029358225209704</v>
       </c>
       <c r="D12">
-        <v>1.107390384351289</v>
+        <v>1.099768225209703</v>
       </c>
       <c r="E12">
-        <v>0.08210000000000001</v>
+        <v>0.09341000000000001</v>
       </c>
       <c r="F12">
-        <v>0.1131</v>
+        <v>0.12441</v>
       </c>
       <c r="G12">
         <v>0.054</v>
@@ -2265,45 +2265,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M12">
-        <v>0.008572980000000001</v>
+        <v>0.0111969</v>
       </c>
       <c r="N12">
-        <v>0.01009368666666666</v>
+        <v>0.007469766666666664</v>
       </c>
       <c r="O12">
-        <v>0.002927169133333333</v>
+        <v>0.002166232333333332</v>
       </c>
       <c r="P12">
-        <v>0.007166517533333331</v>
+        <v>0.005303534333333332</v>
       </c>
       <c r="Q12">
-        <v>0.01116651753333333</v>
+        <v>0.009303534333333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1784124891516428</v>
+        <v>0.1795020049675822</v>
       </c>
       <c r="T12">
-        <v>0.8110414754226837</v>
+        <v>0.8177048185248963</v>
       </c>
       <c r="U12">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V12">
         <v>0.29</v>
       </c>
       <c r="W12">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.177383671333266</v>
+        <v>1.667128103909713</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1667857844211482</v>
+        <v>0.1666103286058178</v>
       </c>
       <c r="C13">
-        <v>1.029358225209704</v>
+        <v>1.019645445686259</v>
       </c>
       <c r="D13">
-        <v>1.099768225209703</v>
+        <v>1.101365445686259</v>
       </c>
       <c r="E13">
-        <v>0.09341000000000001</v>
+        <v>0.10472</v>
       </c>
       <c r="F13">
-        <v>0.12441</v>
+        <v>0.13572</v>
       </c>
       <c r="G13">
         <v>0.054</v>
@@ -2347,28 +2347,28 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M13">
-        <v>0.0111969</v>
+        <v>0.0122148</v>
       </c>
       <c r="N13">
-        <v>0.007469766666666664</v>
+        <v>0.006451866666666665</v>
       </c>
       <c r="O13">
-        <v>0.002166232333333332</v>
+        <v>0.001871041333333333</v>
       </c>
       <c r="P13">
-        <v>0.005303534333333332</v>
+        <v>0.004580825333333332</v>
       </c>
       <c r="Q13">
-        <v>0.009303534333333334</v>
+        <v>0.008580825333333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1795020049675822</v>
+        <v>0.1806162825066112</v>
       </c>
       <c r="T13">
-        <v>0.8177048185248963</v>
+        <v>0.8245196012430681</v>
       </c>
       <c r="U13">
         <v>0.09</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>1.667128103909713</v>
+        <v>1.528200761917237</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1666103286058178</v>
+        <v>0.1730518786956651</v>
       </c>
       <c r="C14">
-        <v>1.019645445686259</v>
+        <v>0.9525838076096047</v>
       </c>
       <c r="D14">
-        <v>1.101365445686259</v>
+        <v>1.045613807609605</v>
       </c>
       <c r="E14">
-        <v>0.10472</v>
+        <v>0.11603</v>
       </c>
       <c r="F14">
-        <v>0.13572</v>
+        <v>0.14703</v>
       </c>
       <c r="G14">
         <v>0.054</v>
@@ -2429,45 +2429,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M14">
-        <v>0.0122148</v>
+        <v>0.021584004</v>
       </c>
       <c r="N14">
-        <v>0.006451866666666665</v>
+        <v>-0.002917337333333336</v>
       </c>
       <c r="O14">
-        <v>0.001871041333333333</v>
+        <v>-0.0008460278266666673</v>
       </c>
       <c r="P14">
-        <v>0.004580825333333332</v>
+        <v>-0.002071309506666668</v>
       </c>
       <c r="Q14">
-        <v>0.008580825333333333</v>
+        <v>0.001928690493333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1806162825066112</v>
+        <v>0.1824760959563102</v>
       </c>
       <c r="T14">
-        <v>0.8245196012430681</v>
+        <v>0.8358939887830686</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.29</v>
+        <v>0.2508030175185907</v>
       </c>
       <c r="W14">
-        <v>0.0639</v>
+        <v>0.1099821170282709</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.528200761917237</v>
+        <v>0.8648379914434163</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1730518786956651</v>
+        <v>0.1740618786956651</v>
       </c>
       <c r="C15">
-        <v>0.9525838076096047</v>
+        <v>0.9330401067124617</v>
       </c>
       <c r="D15">
-        <v>1.045613807609605</v>
+        <v>1.037380106712462</v>
       </c>
       <c r="E15">
-        <v>0.11603</v>
+        <v>0.12734</v>
       </c>
       <c r="F15">
-        <v>0.14703</v>
+        <v>0.15834</v>
       </c>
       <c r="G15">
         <v>0.054</v>
@@ -2511,37 +2511,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M15">
-        <v>0.021584004</v>
+        <v>0.023244312</v>
       </c>
       <c r="N15">
-        <v>-0.002917337333333336</v>
+        <v>-0.004577645333333338</v>
       </c>
       <c r="O15">
-        <v>-0.0008460278266666673</v>
+        <v>-0.001327517146666668</v>
       </c>
       <c r="P15">
-        <v>-0.002071309506666668</v>
+        <v>-0.003250128186666671</v>
       </c>
       <c r="Q15">
-        <v>0.001928690493333334</v>
+        <v>0.0007498718133333313</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1824760959563102</v>
+        <v>0.1840653528860348</v>
       </c>
       <c r="T15">
-        <v>0.8358939887830686</v>
+        <v>0.8456136863270579</v>
       </c>
       <c r="U15">
         <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.2508030175185907</v>
+        <v>0.2328885162672628</v>
       </c>
       <c r="W15">
-        <v>0.1099821170282709</v>
+        <v>0.1126119658119658</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.8648379914434163</v>
+        <v>0.803063849197458</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1740618786956651</v>
+        <v>0.1842496183621033</v>
       </c>
       <c r="C16">
-        <v>0.9330401067124617</v>
+        <v>0.8453950572745701</v>
       </c>
       <c r="D16">
-        <v>1.037380106712462</v>
+        <v>0.9610450572745701</v>
       </c>
       <c r="E16">
-        <v>0.12734</v>
+        <v>0.13865</v>
       </c>
       <c r="F16">
-        <v>0.15834</v>
+        <v>0.16965</v>
       </c>
       <c r="G16">
         <v>0.054</v>
@@ -2593,45 +2593,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M16">
-        <v>0.023244312</v>
+        <v>0.03406572000000001</v>
       </c>
       <c r="N16">
-        <v>-0.004577645333333338</v>
+        <v>-0.01539905333333334</v>
       </c>
       <c r="O16">
-        <v>-0.001327517146666668</v>
+        <v>-0.004465725466666669</v>
       </c>
       <c r="P16">
-        <v>-0.003250128186666671</v>
+        <v>-0.01093332786666667</v>
       </c>
       <c r="Q16">
-        <v>0.0007498718133333313</v>
+        <v>-0.006933327866666672</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1840653528860348</v>
+        <v>0.1869599331157978</v>
       </c>
       <c r="T16">
-        <v>0.8456136863270579</v>
+        <v>0.8633165786812748</v>
       </c>
       <c r="U16">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.2328885162672628</v>
+        <v>0.1589085254423899</v>
       </c>
       <c r="W16">
-        <v>0.1126119658119658</v>
+        <v>0.1688911680911681</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.803063849197458</v>
+        <v>0.5479604325599653</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1842496183621033</v>
+        <v>0.1857996183621033</v>
       </c>
       <c r="C17">
-        <v>0.8453950572745702</v>
+        <v>0.8234448865640849</v>
       </c>
       <c r="D17">
-        <v>0.9610450572745701</v>
+        <v>0.9504048865640848</v>
       </c>
       <c r="E17">
-        <v>0.13865</v>
+        <v>0.14996</v>
       </c>
       <c r="F17">
-        <v>0.16965</v>
+        <v>0.18096</v>
       </c>
       <c r="G17">
         <v>0.054</v>
@@ -2675,37 +2675,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M17">
-        <v>0.03406572</v>
+        <v>0.03633676800000001</v>
       </c>
       <c r="N17">
-        <v>-0.01539905333333334</v>
+        <v>-0.01767010133333334</v>
       </c>
       <c r="O17">
-        <v>-0.004465725466666667</v>
+        <v>-0.005124329386666669</v>
       </c>
       <c r="P17">
-        <v>-0.01093332786666667</v>
+        <v>-0.01254577194666667</v>
       </c>
       <c r="Q17">
-        <v>-0.006933327866666667</v>
+        <v>-0.008545771946666671</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1869599331157978</v>
+        <v>0.1886404085100334</v>
       </c>
       <c r="T17">
-        <v>0.8633165786812748</v>
+        <v>0.8735941569989089</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.15890852544239</v>
+        <v>0.1489767426022406</v>
       </c>
       <c r="W17">
-        <v>0.1688911680911681</v>
+        <v>0.1708854700854701</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5479604325599654</v>
+        <v>0.5137129055249675</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1857996183621033</v>
+        <v>0.1937344993351627</v>
       </c>
       <c r="C18">
-        <v>0.8234448865640849</v>
+        <v>0.7611572600807978</v>
       </c>
       <c r="D18">
-        <v>0.9504048865640848</v>
+        <v>0.8994272600807978</v>
       </c>
       <c r="E18">
-        <v>0.14996</v>
+        <v>0.16127</v>
       </c>
       <c r="F18">
-        <v>0.18096</v>
+        <v>0.19227</v>
       </c>
       <c r="G18">
         <v>0.054</v>
@@ -2757,45 +2757,45 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M18">
-        <v>0.03633676800000001</v>
+        <v>0.04533726600000001</v>
       </c>
       <c r="N18">
-        <v>-0.01767010133333334</v>
+        <v>-0.02667059933333334</v>
       </c>
       <c r="O18">
-        <v>-0.005124329386666669</v>
+        <v>-0.007734473806666669</v>
       </c>
       <c r="P18">
-        <v>-0.01254577194666667</v>
+        <v>-0.01893612552666667</v>
       </c>
       <c r="Q18">
-        <v>-0.008545771946666671</v>
+        <v>-0.01493612552666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1886404085100334</v>
+        <v>0.1908853302668523</v>
       </c>
       <c r="T18">
-        <v>0.8735941569989089</v>
+        <v>0.887323819005154</v>
       </c>
       <c r="U18">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.1489767426022406</v>
+        <v>0.1194014066338568</v>
       </c>
       <c r="W18">
-        <v>0.1708854700854701</v>
+        <v>0.2076451483157366</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.5137129055249675</v>
+        <v>0.4117289883926097</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1937344993351627</v>
+        <v>0.1956344993351626</v>
       </c>
       <c r="C19">
-        <v>0.7611572600807978</v>
+        <v>0.7384419308559784</v>
       </c>
       <c r="D19">
-        <v>0.8994272600807978</v>
+        <v>0.8880219308559784</v>
       </c>
       <c r="E19">
-        <v>0.16127</v>
+        <v>0.17258</v>
       </c>
       <c r="F19">
-        <v>0.19227</v>
+        <v>0.20358</v>
       </c>
       <c r="G19">
         <v>0.054</v>
@@ -2839,37 +2839,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M19">
-        <v>0.04533726600000001</v>
+        <v>0.048004164</v>
       </c>
       <c r="N19">
-        <v>-0.02667059933333334</v>
+        <v>-0.02933749733333334</v>
       </c>
       <c r="O19">
-        <v>-0.007734473806666669</v>
+        <v>-0.008507874226666667</v>
       </c>
       <c r="P19">
-        <v>-0.01893612552666667</v>
+        <v>-0.02082962310666667</v>
       </c>
       <c r="Q19">
-        <v>-0.01493612552666667</v>
+        <v>-0.01682962310666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1908853302668523</v>
+        <v>0.1926546635627895</v>
       </c>
       <c r="T19">
-        <v>0.887323819005154</v>
+        <v>0.8981448411881435</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.1194014066338568</v>
+        <v>0.1127679951541981</v>
       </c>
       <c r="W19">
-        <v>0.2076451483157366</v>
+        <v>0.2092093067426401</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.4117289883926097</v>
+        <v>0.3888551557041315</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1956344993351627</v>
+        <v>0.1975344993351627</v>
       </c>
       <c r="C20">
-        <v>0.7384419308559783</v>
+        <v>0.716012233779709</v>
       </c>
       <c r="D20">
-        <v>0.8880219308559782</v>
+        <v>0.876902233779709</v>
       </c>
       <c r="E20">
-        <v>0.17258</v>
+        <v>0.18389</v>
       </c>
       <c r="F20">
-        <v>0.20358</v>
+        <v>0.21489</v>
       </c>
       <c r="G20">
         <v>0.054</v>
@@ -2921,37 +2921,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M20">
-        <v>0.048004164</v>
+        <v>0.050671062</v>
       </c>
       <c r="N20">
-        <v>-0.02933749733333333</v>
+        <v>-0.03200439533333334</v>
       </c>
       <c r="O20">
-        <v>-0.008507874226666665</v>
+        <v>-0.009281274646666667</v>
       </c>
       <c r="P20">
-        <v>-0.02082962310666667</v>
+        <v>-0.02272312068666667</v>
       </c>
       <c r="Q20">
-        <v>-0.01682962310666666</v>
+        <v>-0.01872312068666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1926546635627895</v>
+        <v>0.1944676841006018</v>
       </c>
       <c r="T20">
-        <v>0.8981448411881435</v>
+        <v>0.9092330491040466</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.1127679951541981</v>
+        <v>0.1068328375145035</v>
       </c>
       <c r="W20">
-        <v>0.2092093067426401</v>
+        <v>0.2106088169140801</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3888551557041315</v>
+        <v>0.3683890948775983</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1975344993351627</v>
+        <v>0.1994344993351627</v>
       </c>
       <c r="C21">
-        <v>0.716012233779709</v>
+        <v>0.6938575716016737</v>
       </c>
       <c r="D21">
-        <v>0.876902233779709</v>
+        <v>0.8660575716016736</v>
       </c>
       <c r="E21">
-        <v>0.18389</v>
+        <v>0.1952</v>
       </c>
       <c r="F21">
-        <v>0.21489</v>
+        <v>0.2262</v>
       </c>
       <c r="G21">
         <v>0.054</v>
@@ -3003,37 +3003,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M21">
-        <v>0.050671062</v>
+        <v>0.05333796</v>
       </c>
       <c r="N21">
-        <v>-0.03200439533333334</v>
+        <v>-0.03467129333333334</v>
       </c>
       <c r="O21">
-        <v>-0.009281274646666667</v>
+        <v>-0.01005467506666667</v>
       </c>
       <c r="P21">
-        <v>-0.02272312068666667</v>
+        <v>-0.02461661826666667</v>
       </c>
       <c r="Q21">
-        <v>-0.01872312068666667</v>
+        <v>-0.02061661826666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1944676841006018</v>
+        <v>0.1963260301518593</v>
       </c>
       <c r="T21">
-        <v>0.9092330491040466</v>
+        <v>0.9205984622178472</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.1068328375145035</v>
+        <v>0.1014911956387783</v>
       </c>
       <c r="W21">
-        <v>0.2106088169140801</v>
+        <v>0.2118683760683761</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3683890948775983</v>
+        <v>0.3499696401337183</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1994344993351627</v>
+        <v>0.2013344993351627</v>
       </c>
       <c r="C22">
-        <v>0.6938575716016737</v>
+        <v>0.6719678648930208</v>
       </c>
       <c r="D22">
-        <v>0.8660575716016736</v>
+        <v>0.8554778648930208</v>
       </c>
       <c r="E22">
-        <v>0.1952</v>
+        <v>0.20651</v>
       </c>
       <c r="F22">
-        <v>0.2262</v>
+        <v>0.23751</v>
       </c>
       <c r="G22">
         <v>0.054</v>
@@ -3085,37 +3085,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M22">
-        <v>0.05333796</v>
+        <v>0.05600485800000001</v>
       </c>
       <c r="N22">
-        <v>-0.03467129333333334</v>
+        <v>-0.03733819133333335</v>
       </c>
       <c r="O22">
-        <v>-0.01005467506666667</v>
+        <v>-0.01082807548666667</v>
       </c>
       <c r="P22">
-        <v>-0.02461661826666667</v>
+        <v>-0.02651011584666668</v>
       </c>
       <c r="Q22">
-        <v>-0.02061661826666667</v>
+        <v>-0.02251011584666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1963260301518593</v>
+        <v>0.1982314229385917</v>
       </c>
       <c r="T22">
-        <v>0.9205984622178472</v>
+        <v>0.9322516073092125</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.1014911956387783</v>
+        <v>0.09665828156074123</v>
       </c>
       <c r="W22">
-        <v>0.2118683760683761</v>
+        <v>0.2130079772079772</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3499696401337183</v>
+        <v>0.3333044191749698</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2013344993351626</v>
+        <v>0.2032344993351627</v>
       </c>
       <c r="C23">
-        <v>0.6719678648930211</v>
+        <v>0.6503335207996949</v>
       </c>
       <c r="D23">
-        <v>0.855477864893021</v>
+        <v>0.8451535207996949</v>
       </c>
       <c r="E23">
-        <v>0.20651</v>
+        <v>0.21782</v>
       </c>
       <c r="F23">
-        <v>0.23751</v>
+        <v>0.24882</v>
       </c>
       <c r="G23">
         <v>0.054</v>
@@ -3167,37 +3167,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M23">
-        <v>0.056004858</v>
+        <v>0.05867175600000001</v>
       </c>
       <c r="N23">
-        <v>-0.03733819133333334</v>
+        <v>-0.04000508933333334</v>
       </c>
       <c r="O23">
-        <v>-0.01082807548666667</v>
+        <v>-0.01160147590666667</v>
       </c>
       <c r="P23">
-        <v>-0.02651011584666667</v>
+        <v>-0.02840361342666667</v>
       </c>
       <c r="Q23">
-        <v>-0.02251011584666667</v>
+        <v>-0.02440361342666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1982314229385917</v>
+        <v>0.2001856719506249</v>
       </c>
       <c r="T23">
-        <v>0.9322516073092123</v>
+        <v>0.9442035509926638</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.09665828156074124</v>
+        <v>0.09226472330798029</v>
       </c>
       <c r="W23">
-        <v>0.2130079772079772</v>
+        <v>0.2140439782439783</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3333044191749699</v>
+        <v>0.3181542183033803</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2032344993351627</v>
+        <v>0.2051344993351627</v>
       </c>
       <c r="C24">
-        <v>0.6503335207996949</v>
+        <v>0.6289454040313882</v>
       </c>
       <c r="D24">
-        <v>0.8451535207996949</v>
+        <v>0.8350754040313881</v>
       </c>
       <c r="E24">
-        <v>0.21782</v>
+        <v>0.22913</v>
       </c>
       <c r="F24">
-        <v>0.24882</v>
+        <v>0.26013</v>
       </c>
       <c r="G24">
         <v>0.054</v>
@@ -3249,37 +3249,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M24">
-        <v>0.05867175600000001</v>
+        <v>0.06133865400000001</v>
       </c>
       <c r="N24">
-        <v>-0.04000508933333334</v>
+        <v>-0.04267198733333334</v>
       </c>
       <c r="O24">
-        <v>-0.01160147590666667</v>
+        <v>-0.01237487632666667</v>
       </c>
       <c r="P24">
-        <v>-0.02840361342666667</v>
+        <v>-0.03029711100666668</v>
       </c>
       <c r="Q24">
-        <v>-0.02440361342666667</v>
+        <v>-0.02629711100666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2001856719506249</v>
+        <v>0.2021906806772564</v>
       </c>
       <c r="T24">
-        <v>0.9442035509926638</v>
+        <v>0.9564659347717893</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.09226472330798029</v>
+        <v>0.08825321359893766</v>
       </c>
       <c r="W24">
-        <v>0.2140439782439783</v>
+        <v>0.2149898922333705</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3181542183033803</v>
+        <v>0.3043214262032333</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2051344993351627</v>
+        <v>0.2070344993351627</v>
       </c>
       <c r="C25">
-        <v>0.6289454040313882</v>
+        <v>0.6077948099017075</v>
       </c>
       <c r="D25">
-        <v>0.8350754040313881</v>
+        <v>0.8252348099017075</v>
       </c>
       <c r="E25">
-        <v>0.22913</v>
+        <v>0.24044</v>
       </c>
       <c r="F25">
-        <v>0.26013</v>
+        <v>0.27144</v>
       </c>
       <c r="G25">
         <v>0.054</v>
@@ -3331,37 +3331,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M25">
-        <v>0.06133865400000001</v>
+        <v>0.06400555200000001</v>
       </c>
       <c r="N25">
-        <v>-0.04267198733333334</v>
+        <v>-0.04533888533333334</v>
       </c>
       <c r="O25">
-        <v>-0.01237487632666667</v>
+        <v>-0.01314827674666667</v>
       </c>
       <c r="P25">
-        <v>-0.03029711100666668</v>
+        <v>-0.03219060858666668</v>
       </c>
       <c r="Q25">
-        <v>-0.02629711100666667</v>
+        <v>-0.02819060858666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2021906806772564</v>
+        <v>0.2042484527914308</v>
       </c>
       <c r="T25">
-        <v>0.9564659347717893</v>
+        <v>0.9690510128608918</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.08825321359893766</v>
+        <v>0.08457599636564858</v>
       </c>
       <c r="W25">
-        <v>0.2149898922333705</v>
+        <v>0.2158569800569801</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3043214262032333</v>
+        <v>0.2916413667780986</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2070344993351627</v>
+        <v>0.2089344993351626</v>
       </c>
       <c r="C26">
-        <v>0.6077948099017075</v>
+        <v>0.5868734392523156</v>
       </c>
       <c r="D26">
-        <v>0.8252348099017075</v>
+        <v>0.8156234392523156</v>
       </c>
       <c r="E26">
-        <v>0.24044</v>
+        <v>0.25175</v>
       </c>
       <c r="F26">
-        <v>0.27144</v>
+        <v>0.28275</v>
       </c>
       <c r="G26">
         <v>0.054</v>
@@ -3413,37 +3413,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M26">
-        <v>0.06400555200000001</v>
+        <v>0.06667245000000001</v>
       </c>
       <c r="N26">
-        <v>-0.04533888533333334</v>
+        <v>-0.04800578333333334</v>
       </c>
       <c r="O26">
-        <v>-0.01314827674666667</v>
+        <v>-0.01392167716666667</v>
       </c>
       <c r="P26">
-        <v>-0.03219060858666668</v>
+        <v>-0.03408410616666668</v>
       </c>
       <c r="Q26">
-        <v>-0.02819060858666667</v>
+        <v>-0.03008410616666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2042484527914308</v>
+        <v>0.2063610988286499</v>
       </c>
       <c r="T26">
-        <v>0.9690510128608918</v>
+        <v>0.9819716930323704</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.08457599636564858</v>
+        <v>0.08119295651102264</v>
       </c>
       <c r="W26">
-        <v>0.2158569800569801</v>
+        <v>0.2166547008547009</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2916413667780986</v>
+        <v>0.2799757121069747</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2089344993351626</v>
+        <v>0.2108344993351627</v>
       </c>
       <c r="C27">
-        <v>0.5868734392523156</v>
+        <v>0.5661733751092286</v>
       </c>
       <c r="D27">
-        <v>0.8156234392523156</v>
+        <v>0.8062333751092285</v>
       </c>
       <c r="E27">
-        <v>0.25175</v>
+        <v>0.26306</v>
       </c>
       <c r="F27">
-        <v>0.28275</v>
+        <v>0.29406</v>
       </c>
       <c r="G27">
         <v>0.054</v>
@@ -3495,37 +3495,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M27">
-        <v>0.06667245000000001</v>
+        <v>0.069339348</v>
       </c>
       <c r="N27">
-        <v>-0.04800578333333334</v>
+        <v>-0.05067268133333333</v>
       </c>
       <c r="O27">
-        <v>-0.01392167716666667</v>
+        <v>-0.01469507758666666</v>
       </c>
       <c r="P27">
-        <v>-0.03408410616666668</v>
+        <v>-0.03597760374666667</v>
       </c>
       <c r="Q27">
-        <v>-0.03008410616666667</v>
+        <v>-0.03197760374666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2063610988286499</v>
+        <v>0.2085308434074155</v>
       </c>
       <c r="T27">
-        <v>0.9819716930323704</v>
+        <v>0.995241580776051</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.08119295651102264</v>
+        <v>0.07807015049136794</v>
       </c>
       <c r="W27">
-        <v>0.2166547008547009</v>
+        <v>0.2173910585141355</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2799757121069747</v>
+        <v>0.2692074154874757</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2108344993351627</v>
+        <v>0.2127344993351626</v>
       </c>
       <c r="C28">
-        <v>0.5661733751092286</v>
+        <v>0.5456870609332597</v>
       </c>
       <c r="D28">
-        <v>0.8062333751092285</v>
+        <v>0.7970570609332597</v>
       </c>
       <c r="E28">
-        <v>0.26306</v>
+        <v>0.27437</v>
       </c>
       <c r="F28">
-        <v>0.29406</v>
+        <v>0.30537</v>
       </c>
       <c r="G28">
         <v>0.054</v>
@@ -3577,37 +3577,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M28">
-        <v>0.069339348</v>
+        <v>0.07200624600000001</v>
       </c>
       <c r="N28">
-        <v>-0.05067268133333333</v>
+        <v>-0.05333957933333335</v>
       </c>
       <c r="O28">
-        <v>-0.01469507758666666</v>
+        <v>-0.01546847800666667</v>
       </c>
       <c r="P28">
-        <v>-0.03597760374666667</v>
+        <v>-0.03787110132666668</v>
       </c>
       <c r="Q28">
-        <v>-0.03197760374666667</v>
+        <v>-0.03387110132666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2085308434074155</v>
+        <v>0.2107600330431335</v>
       </c>
       <c r="T28">
-        <v>0.995241580776051</v>
+        <v>1.008875027088052</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.07807015049136794</v>
+        <v>0.07517866343613207</v>
       </c>
       <c r="W28">
-        <v>0.2173910585141355</v>
+        <v>0.2180728711617601</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2692074154874757</v>
+        <v>0.259236770469421</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2127344993351626</v>
+        <v>0.2146344993351627</v>
       </c>
       <c r="C29">
-        <v>0.5456870609332597</v>
+        <v>0.5254072803390291</v>
       </c>
       <c r="D29">
-        <v>0.7970570609332597</v>
+        <v>0.788087280339029</v>
       </c>
       <c r="E29">
-        <v>0.27437</v>
+        <v>0.28568</v>
       </c>
       <c r="F29">
-        <v>0.30537</v>
+        <v>0.31668</v>
       </c>
       <c r="G29">
         <v>0.054</v>
@@ -3659,37 +3659,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M29">
-        <v>0.07200624600000001</v>
+        <v>0.07467314400000001</v>
       </c>
       <c r="N29">
-        <v>-0.05333957933333335</v>
+        <v>-0.05600647733333335</v>
       </c>
       <c r="O29">
-        <v>-0.01546847800666667</v>
+        <v>-0.01624187842666667</v>
       </c>
       <c r="P29">
-        <v>-0.03787110132666668</v>
+        <v>-0.03976459890666668</v>
       </c>
       <c r="Q29">
-        <v>-0.03387110132666667</v>
+        <v>-0.03576459890666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2107600330431335</v>
+        <v>0.213051144613177</v>
       </c>
       <c r="T29">
-        <v>1.008875027088052</v>
+        <v>1.022887180242052</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.07517866343613207</v>
+        <v>0.07249371117055593</v>
       </c>
       <c r="W29">
-        <v>0.2180728711617601</v>
+        <v>0.2187059829059829</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.259236770469421</v>
+        <v>0.2499783143812274</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2146344993351627</v>
+        <v>0.2165344993351627</v>
       </c>
       <c r="C30">
-        <v>0.5254072803390291</v>
+        <v>0.5053271381681446</v>
       </c>
       <c r="D30">
-        <v>0.788087280339029</v>
+        <v>0.7793171381681445</v>
       </c>
       <c r="E30">
-        <v>0.28568</v>
+        <v>0.2969900000000001</v>
       </c>
       <c r="F30">
-        <v>0.31668</v>
+        <v>0.3279900000000001</v>
       </c>
       <c r="G30">
         <v>0.054</v>
@@ -3741,37 +3741,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M30">
-        <v>0.07467314400000001</v>
+        <v>0.07734004200000001</v>
       </c>
       <c r="N30">
-        <v>-0.05600647733333335</v>
+        <v>-0.05867337533333335</v>
       </c>
       <c r="O30">
-        <v>-0.01624187842666667</v>
+        <v>-0.01701527884666667</v>
       </c>
       <c r="P30">
-        <v>-0.03976459890666668</v>
+        <v>-0.04165809648666668</v>
       </c>
       <c r="Q30">
-        <v>-0.03576459890666667</v>
+        <v>-0.03765809648666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.213051144613177</v>
+        <v>0.2154067945373062</v>
       </c>
       <c r="T30">
-        <v>1.022887180242052</v>
+        <v>1.037294041935602</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.07249371117055593</v>
+        <v>0.06999392802674366</v>
       </c>
       <c r="W30">
-        <v>0.2187059829059829</v>
+        <v>0.2192954317712938</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2499783143812274</v>
+        <v>0.2413583725060127</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2165344993351626</v>
+        <v>0.2184344993351627</v>
       </c>
       <c r="C31">
-        <v>0.5053271381681446</v>
+        <v>0.485440042812223</v>
       </c>
       <c r="D31">
-        <v>0.7793171381681445</v>
+        <v>0.770740042812223</v>
       </c>
       <c r="E31">
-        <v>0.29699</v>
+        <v>0.3083</v>
       </c>
       <c r="F31">
-        <v>0.32799</v>
+        <v>0.3393</v>
       </c>
       <c r="G31">
         <v>0.054</v>
@@ -3823,37 +3823,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M31">
-        <v>0.077340042</v>
+        <v>0.08000694</v>
       </c>
       <c r="N31">
-        <v>-0.05867337533333333</v>
+        <v>-0.06134027333333333</v>
       </c>
       <c r="O31">
-        <v>-0.01701527884666667</v>
+        <v>-0.01778867926666667</v>
       </c>
       <c r="P31">
-        <v>-0.04165809648666667</v>
+        <v>-0.04355159406666667</v>
       </c>
       <c r="Q31">
-        <v>-0.03765809648666667</v>
+        <v>-0.03955159406666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2154067945373062</v>
+        <v>0.2178297487449821</v>
       </c>
       <c r="T31">
-        <v>1.037294041935602</v>
+        <v>1.052112528248968</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.06999392802674367</v>
+        <v>0.06766079709251888</v>
       </c>
       <c r="W31">
-        <v>0.2192954317712938</v>
+        <v>0.219845584045584</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2413583725060127</v>
+        <v>0.233313093422479</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2184344993351627</v>
+        <v>0.2203344993351626</v>
       </c>
       <c r="C32">
-        <v>0.485440042812223</v>
+        <v>0.465739689690511</v>
       </c>
       <c r="D32">
-        <v>0.770740042812223</v>
+        <v>0.762349689690511</v>
       </c>
       <c r="E32">
-        <v>0.3083</v>
+        <v>0.3196099999999999</v>
       </c>
       <c r="F32">
-        <v>0.3393</v>
+        <v>0.35061</v>
       </c>
       <c r="G32">
         <v>0.054</v>
@@ -3905,37 +3905,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M32">
-        <v>0.08000694</v>
+        <v>0.082673838</v>
       </c>
       <c r="N32">
-        <v>-0.06134027333333333</v>
+        <v>-0.06400717133333333</v>
       </c>
       <c r="O32">
-        <v>-0.01778867926666667</v>
+        <v>-0.01856207968666667</v>
       </c>
       <c r="P32">
-        <v>-0.04355159406666667</v>
+        <v>-0.04544509164666667</v>
       </c>
       <c r="Q32">
-        <v>-0.03955159406666667</v>
+        <v>-0.04144509164666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2178297487449821</v>
+        <v>0.2203229335094021</v>
       </c>
       <c r="T32">
-        <v>1.052112528248968</v>
+        <v>1.06736053590475</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.06766079709251888</v>
+        <v>0.06547819073469568</v>
       </c>
       <c r="W32">
-        <v>0.219845584045584</v>
+        <v>0.2203602426247588</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.233313093422479</v>
+        <v>0.2257868646023989</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2203344993351626</v>
+        <v>0.2222344993351626</v>
       </c>
       <c r="C33">
-        <v>0.465739689690511</v>
+        <v>0.4462200457950708</v>
       </c>
       <c r="D33">
-        <v>0.762349689690511</v>
+        <v>0.7541400457950708</v>
       </c>
       <c r="E33">
-        <v>0.3196099999999999</v>
+        <v>0.33092</v>
       </c>
       <c r="F33">
-        <v>0.35061</v>
+        <v>0.36192</v>
       </c>
       <c r="G33">
         <v>0.054</v>
@@ -3987,37 +3987,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M33">
-        <v>0.082673838</v>
+        <v>0.08534073600000001</v>
       </c>
       <c r="N33">
-        <v>-0.06400717133333333</v>
+        <v>-0.06667406933333335</v>
       </c>
       <c r="O33">
-        <v>-0.01856207968666667</v>
+        <v>-0.01933548010666667</v>
       </c>
       <c r="P33">
-        <v>-0.04544509164666667</v>
+        <v>-0.04733858922666668</v>
       </c>
       <c r="Q33">
-        <v>-0.04144509164666667</v>
+        <v>-0.04333858922666668</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2203229335094021</v>
+        <v>0.2228894472374816</v>
       </c>
       <c r="T33">
-        <v>1.06736053590475</v>
+        <v>1.083057014373938</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.06547819073469568</v>
+        <v>0.06343199727423644</v>
       </c>
       <c r="W33">
-        <v>0.2203602426247588</v>
+        <v>0.220842735042735</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2257868646023989</v>
+        <v>0.2187310250835739</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2222344993351626</v>
+        <v>0.2241344993351627</v>
       </c>
       <c r="C34">
-        <v>0.4462200457950708</v>
+        <v>0.4268753352239114</v>
       </c>
       <c r="D34">
-        <v>0.7541400457950708</v>
+        <v>0.7461053352239113</v>
       </c>
       <c r="E34">
-        <v>0.33092</v>
+        <v>0.34223</v>
       </c>
       <c r="F34">
-        <v>0.36192</v>
+        <v>0.37323</v>
       </c>
       <c r="G34">
         <v>0.054</v>
@@ -4069,37 +4069,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M34">
-        <v>0.08534073600000001</v>
+        <v>0.088007634</v>
       </c>
       <c r="N34">
-        <v>-0.06667406933333335</v>
+        <v>-0.06934096733333334</v>
       </c>
       <c r="O34">
-        <v>-0.01933548010666667</v>
+        <v>-0.02010888052666667</v>
       </c>
       <c r="P34">
-        <v>-0.04733858922666668</v>
+        <v>-0.04923208680666667</v>
       </c>
       <c r="Q34">
-        <v>-0.04333858922666668</v>
+        <v>-0.04523208680666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2228894472374816</v>
+        <v>0.2255325733156529</v>
       </c>
       <c r="T34">
-        <v>1.083057014373938</v>
+        <v>1.099222044439221</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06343199727423644</v>
+        <v>0.06150981553865353</v>
       </c>
       <c r="W34">
-        <v>0.220842735042735</v>
+        <v>0.2212959854959855</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2187310250835739</v>
+        <v>0.2121028122022536</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2241344993351627</v>
+        <v>0.2260344993351626</v>
       </c>
       <c r="C35">
-        <v>0.4268753352239114</v>
+        <v>0.4077000256291637</v>
       </c>
       <c r="D35">
-        <v>0.7461053352239113</v>
+        <v>0.7382400256291637</v>
       </c>
       <c r="E35">
-        <v>0.34223</v>
+        <v>0.3535400000000001</v>
       </c>
       <c r="F35">
-        <v>0.37323</v>
+        <v>0.38454</v>
       </c>
       <c r="G35">
         <v>0.054</v>
@@ -4151,37 +4151,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M35">
-        <v>0.088007634</v>
+        <v>0.09067453200000002</v>
       </c>
       <c r="N35">
-        <v>-0.06934096733333334</v>
+        <v>-0.07200786533333335</v>
       </c>
       <c r="O35">
-        <v>-0.02010888052666667</v>
+        <v>-0.02088228094666667</v>
       </c>
       <c r="P35">
-        <v>-0.04923208680666667</v>
+        <v>-0.05112558438666668</v>
       </c>
       <c r="Q35">
-        <v>-0.04523208680666667</v>
+        <v>-0.04712558438666668</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2255325733156529</v>
+        <v>0.2282557941234658</v>
       </c>
       <c r="T35">
-        <v>1.099222044439221</v>
+        <v>1.115876923900421</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06150981553865353</v>
+        <v>0.05970070331692841</v>
       </c>
       <c r="W35">
-        <v>0.2212959854959855</v>
+        <v>0.2217225741578683</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2121028122022536</v>
+        <v>0.2058644941963049</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2260344993351626</v>
+        <v>0.2279344993351627</v>
       </c>
       <c r="C36">
-        <v>0.4077000256291637</v>
+        <v>0.3886888155134772</v>
       </c>
       <c r="D36">
-        <v>0.7382400256291637</v>
+        <v>0.7305388155134772</v>
       </c>
       <c r="E36">
-        <v>0.3535400000000001</v>
+        <v>0.36485</v>
       </c>
       <c r="F36">
-        <v>0.38454</v>
+        <v>0.39585</v>
       </c>
       <c r="G36">
         <v>0.054</v>
@@ -4233,37 +4233,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M36">
-        <v>0.09067453200000002</v>
+        <v>0.09334143000000002</v>
       </c>
       <c r="N36">
-        <v>-0.07200786533333335</v>
+        <v>-0.07467476333333335</v>
       </c>
       <c r="O36">
-        <v>-0.02088228094666667</v>
+        <v>-0.02165568136666667</v>
       </c>
       <c r="P36">
-        <v>-0.05112558438666668</v>
+        <v>-0.05301908196666668</v>
       </c>
       <c r="Q36">
-        <v>-0.04712558438666668</v>
+        <v>-0.04901908196666668</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2282557941234658</v>
+        <v>0.2310628063407499</v>
       </c>
       <c r="T36">
-        <v>1.115876923900421</v>
+        <v>1.133044261191197</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05970070331692841</v>
+        <v>0.05799496893644474</v>
       </c>
       <c r="W36">
-        <v>0.2217225741578683</v>
+        <v>0.2221247863247863</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2058644941963049</v>
+        <v>0.1999826515049818</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2279344993351627</v>
+        <v>0.2298344993351626</v>
       </c>
       <c r="C37">
-        <v>0.3886888155134772</v>
+        <v>0.3698366223133439</v>
       </c>
       <c r="D37">
-        <v>0.7305388155134772</v>
+        <v>0.7229966223133438</v>
       </c>
       <c r="E37">
-        <v>0.36485</v>
+        <v>0.37616</v>
       </c>
       <c r="F37">
-        <v>0.39585</v>
+        <v>0.40716</v>
       </c>
       <c r="G37">
         <v>0.054</v>
@@ -4315,37 +4315,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M37">
-        <v>0.09334143000000002</v>
+        <v>0.096008328</v>
       </c>
       <c r="N37">
-        <v>-0.07467476333333335</v>
+        <v>-0.07734166133333334</v>
       </c>
       <c r="O37">
-        <v>-0.02165568136666667</v>
+        <v>-0.02242908178666667</v>
       </c>
       <c r="P37">
-        <v>-0.05301908196666668</v>
+        <v>-0.05491257954666667</v>
       </c>
       <c r="Q37">
-        <v>-0.04901908196666668</v>
+        <v>-0.05091257954666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2310628063407499</v>
+        <v>0.2339575376898241</v>
       </c>
       <c r="T37">
-        <v>1.133044261191197</v>
+        <v>1.150748077772309</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.05799496893644474</v>
+        <v>0.05638399757709906</v>
       </c>
       <c r="W37">
-        <v>0.2221247863247863</v>
+        <v>0.22250465337132</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1999826515049818</v>
+        <v>0.1944275778520658</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2298344993351626</v>
+        <v>0.2317344993351627</v>
       </c>
       <c r="C38">
-        <v>0.3698366223133439</v>
+        <v>0.3511385712130521</v>
       </c>
       <c r="D38">
-        <v>0.7229966223133438</v>
+        <v>0.7156085712130521</v>
       </c>
       <c r="E38">
-        <v>0.3761599999999999</v>
+        <v>0.38747</v>
       </c>
       <c r="F38">
-        <v>0.40716</v>
+        <v>0.41847</v>
       </c>
       <c r="G38">
         <v>0.054</v>
@@ -4397,37 +4397,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M38">
-        <v>0.09600832799999999</v>
+        <v>0.098675226</v>
       </c>
       <c r="N38">
-        <v>-0.07734166133333333</v>
+        <v>-0.08000855933333334</v>
       </c>
       <c r="O38">
-        <v>-0.02242908178666666</v>
+        <v>-0.02320248220666667</v>
       </c>
       <c r="P38">
-        <v>-0.05491257954666666</v>
+        <v>-0.05680607712666667</v>
       </c>
       <c r="Q38">
-        <v>-0.05091257954666666</v>
+        <v>-0.05280607712666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2339575376898241</v>
+        <v>0.2369441652722023</v>
       </c>
       <c r="T38">
-        <v>1.150748077772309</v>
+        <v>1.169013920276631</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05638399757709907</v>
+        <v>0.05486010575069098</v>
       </c>
       <c r="W38">
-        <v>0.22250465337132</v>
+        <v>0.2228639870639871</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1944275778520658</v>
+        <v>0.1891727784506586</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2317344993351627</v>
+        <v>0.2336344993351627</v>
       </c>
       <c r="C39">
-        <v>0.3511385712130521</v>
+        <v>0.3325899846375439</v>
       </c>
       <c r="D39">
-        <v>0.7156085712130521</v>
+        <v>0.7083699846375439</v>
       </c>
       <c r="E39">
-        <v>0.38747</v>
+        <v>0.39878</v>
       </c>
       <c r="F39">
-        <v>0.41847</v>
+        <v>0.42978</v>
       </c>
       <c r="G39">
         <v>0.054</v>
@@ -4479,37 +4479,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M39">
-        <v>0.098675226</v>
+        <v>0.101342124</v>
       </c>
       <c r="N39">
-        <v>-0.08000855933333334</v>
+        <v>-0.08267545733333334</v>
       </c>
       <c r="O39">
-        <v>-0.02320248220666667</v>
+        <v>-0.02397588262666667</v>
       </c>
       <c r="P39">
-        <v>-0.05680607712666667</v>
+        <v>-0.05869957470666667</v>
       </c>
       <c r="Q39">
-        <v>-0.05280607712666667</v>
+        <v>-0.05469957470666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2369441652722023</v>
+        <v>0.2400271356798185</v>
       </c>
       <c r="T39">
-        <v>1.169013920276631</v>
+        <v>1.1878689835069</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05486010575069098</v>
+        <v>0.05341641875725174</v>
       </c>
       <c r="W39">
-        <v>0.2228639870639871</v>
+        <v>0.22320440845704</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1891727784506586</v>
+        <v>0.1841945474387991</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2336344993351627</v>
+        <v>0.2355344993351627</v>
       </c>
       <c r="C40">
-        <v>0.3325899846375439</v>
+        <v>0.3141863723765823</v>
       </c>
       <c r="D40">
-        <v>0.7083699846375439</v>
+        <v>0.7012763723765822</v>
       </c>
       <c r="E40">
-        <v>0.39878</v>
+        <v>0.4100900000000001</v>
       </c>
       <c r="F40">
-        <v>0.42978</v>
+        <v>0.44109</v>
       </c>
       <c r="G40">
         <v>0.054</v>
@@ -4561,37 +4561,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M40">
-        <v>0.101342124</v>
+        <v>0.104009022</v>
       </c>
       <c r="N40">
-        <v>-0.08267545733333334</v>
+        <v>-0.08534235533333334</v>
       </c>
       <c r="O40">
-        <v>-0.02397588262666667</v>
+        <v>-0.02474928304666667</v>
       </c>
       <c r="P40">
-        <v>-0.05869957470666667</v>
+        <v>-0.06059307228666667</v>
       </c>
       <c r="Q40">
-        <v>-0.05469957470666667</v>
+        <v>-0.05659307228666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2400271356798185</v>
+        <v>0.2432111870844056</v>
       </c>
       <c r="T40">
-        <v>1.1878689835069</v>
+        <v>1.207342245531603</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05341641875725174</v>
+        <v>0.05204676699424529</v>
       </c>
       <c r="W40">
-        <v>0.22320440845704</v>
+        <v>0.223527372342757</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1841945474387991</v>
+        <v>0.1794716103249837</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2355344993351627</v>
+        <v>0.2374344993351627</v>
       </c>
       <c r="C41">
-        <v>0.3141863723765823</v>
+        <v>0.2959234222964136</v>
       </c>
       <c r="D41">
-        <v>0.7012763723765822</v>
+        <v>0.6943234222964135</v>
       </c>
       <c r="E41">
-        <v>0.4100900000000001</v>
+        <v>0.4214</v>
       </c>
       <c r="F41">
-        <v>0.44109</v>
+        <v>0.4524</v>
       </c>
       <c r="G41">
         <v>0.054</v>
@@ -4643,37 +4643,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M41">
-        <v>0.104009022</v>
+        <v>0.10667592</v>
       </c>
       <c r="N41">
-        <v>-0.08534235533333334</v>
+        <v>-0.08800925333333334</v>
       </c>
       <c r="O41">
-        <v>-0.02474928304666667</v>
+        <v>-0.02552268346666667</v>
       </c>
       <c r="P41">
-        <v>-0.06059307228666667</v>
+        <v>-0.06248656986666667</v>
       </c>
       <c r="Q41">
-        <v>-0.05659307228666667</v>
+        <v>-0.05848656986666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2432111870844056</v>
+        <v>0.2465013735358124</v>
       </c>
       <c r="T41">
-        <v>1.207342245531603</v>
+        <v>1.227464616290463</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05204676699424529</v>
+        <v>0.05074559781938916</v>
       </c>
       <c r="W41">
-        <v>0.223527372342757</v>
+        <v>0.2238341880341881</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1794716103249837</v>
+        <v>0.1749848200668591</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2374344993351627</v>
+        <v>0.2393344993351627</v>
       </c>
       <c r="C42">
-        <v>0.2959234222964136</v>
+        <v>0.2777969915985536</v>
       </c>
       <c r="D42">
-        <v>0.6943234222964135</v>
+        <v>0.6875069915985536</v>
       </c>
       <c r="E42">
-        <v>0.4214</v>
+        <v>0.43271</v>
       </c>
       <c r="F42">
-        <v>0.4524</v>
+        <v>0.46371</v>
       </c>
       <c r="G42">
         <v>0.054</v>
@@ -4725,37 +4725,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M42">
-        <v>0.10667592</v>
+        <v>0.109342818</v>
       </c>
       <c r="N42">
-        <v>-0.08800925333333334</v>
+        <v>-0.09067615133333334</v>
       </c>
       <c r="O42">
-        <v>-0.02552268346666667</v>
+        <v>-0.02629608388666667</v>
       </c>
       <c r="P42">
-        <v>-0.06248656986666667</v>
+        <v>-0.06438006744666668</v>
       </c>
       <c r="Q42">
-        <v>-0.05848656986666667</v>
+        <v>-0.06038006744666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2465013735358124</v>
+        <v>0.2499030917313347</v>
       </c>
       <c r="T42">
-        <v>1.227464616290463</v>
+        <v>1.248269101312335</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05074559781938916</v>
+        <v>0.04950790031159918</v>
       </c>
       <c r="W42">
-        <v>0.2238341880341881</v>
+        <v>0.2241260371065249</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1749848200668591</v>
+        <v>0.170716897626204</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2393344993351627</v>
+        <v>0.2412344993351626</v>
       </c>
       <c r="C43">
-        <v>0.2777969915985536</v>
+        <v>0.2598030985884609</v>
       </c>
       <c r="D43">
-        <v>0.6875069915985536</v>
+        <v>0.6808230985884609</v>
       </c>
       <c r="E43">
-        <v>0.43271</v>
+        <v>0.4440200000000001</v>
       </c>
       <c r="F43">
-        <v>0.46371</v>
+        <v>0.4750200000000001</v>
       </c>
       <c r="G43">
         <v>0.054</v>
@@ -4807,37 +4807,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M43">
-        <v>0.109342818</v>
+        <v>0.112009716</v>
       </c>
       <c r="N43">
-        <v>-0.09067615133333334</v>
+        <v>-0.09334304933333336</v>
       </c>
       <c r="O43">
-        <v>-0.02629608388666667</v>
+        <v>-0.02706948430666667</v>
       </c>
       <c r="P43">
-        <v>-0.06438006744666668</v>
+        <v>-0.06627356502666669</v>
       </c>
       <c r="Q43">
-        <v>-0.06038006744666667</v>
+        <v>-0.06227356502666669</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2499030917313347</v>
+        <v>0.2534221105542886</v>
       </c>
       <c r="T43">
-        <v>1.248269101312335</v>
+        <v>1.269790982369444</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04950790031159918</v>
+        <v>0.04832914078037061</v>
       </c>
       <c r="W43">
-        <v>0.2241260371065249</v>
+        <v>0.2244039886039886</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.170716897626204</v>
+        <v>0.1666522095874849</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2412344993351627</v>
+        <v>0.2431344993351627</v>
       </c>
       <c r="C44">
-        <v>0.259803098588461</v>
+        <v>0.241937914919735</v>
       </c>
       <c r="D44">
-        <v>0.6808230985884609</v>
+        <v>0.6742679149197349</v>
       </c>
       <c r="E44">
-        <v>0.44402</v>
+        <v>0.45533</v>
       </c>
       <c r="F44">
-        <v>0.47502</v>
+        <v>0.48633</v>
       </c>
       <c r="G44">
         <v>0.054</v>
@@ -4889,37 +4889,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M44">
-        <v>0.112009716</v>
+        <v>0.114676614</v>
       </c>
       <c r="N44">
-        <v>-0.09334304933333334</v>
+        <v>-0.09600994733333333</v>
       </c>
       <c r="O44">
-        <v>-0.02706948430666667</v>
+        <v>-0.02784288472666666</v>
       </c>
       <c r="P44">
-        <v>-0.06627356502666668</v>
+        <v>-0.06816706260666666</v>
       </c>
       <c r="Q44">
-        <v>-0.06227356502666667</v>
+        <v>-0.06416706260666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2534221105542886</v>
+        <v>0.2570646037219078</v>
       </c>
       <c r="T44">
-        <v>1.269790982369444</v>
+        <v>1.292068017147856</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04832914078037062</v>
+        <v>0.04720520727385038</v>
       </c>
       <c r="W44">
-        <v>0.2244039886039886</v>
+        <v>0.2246690121248261</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1666522095874849</v>
+        <v>0.1627765768063807</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2431344993351627</v>
+        <v>0.2450344993351626</v>
       </c>
       <c r="C45">
-        <v>0.241937914919735</v>
+        <v>0.2241977582820919</v>
       </c>
       <c r="D45">
-        <v>0.6742679149197349</v>
+        <v>0.6678377582820919</v>
       </c>
       <c r="E45">
-        <v>0.45533</v>
+        <v>0.4666400000000001</v>
       </c>
       <c r="F45">
-        <v>0.48633</v>
+        <v>0.49764</v>
       </c>
       <c r="G45">
         <v>0.054</v>
@@ -4971,37 +4971,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M45">
-        <v>0.114676614</v>
+        <v>0.117343512</v>
       </c>
       <c r="N45">
-        <v>-0.09600994733333333</v>
+        <v>-0.09867684533333335</v>
       </c>
       <c r="O45">
-        <v>-0.02784288472666666</v>
+        <v>-0.02861628514666667</v>
       </c>
       <c r="P45">
-        <v>-0.06816706260666666</v>
+        <v>-0.07006056018666668</v>
       </c>
       <c r="Q45">
-        <v>-0.06416706260666666</v>
+        <v>-0.06606056018666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2570646037219078</v>
+        <v>0.2608371859312275</v>
       </c>
       <c r="T45">
-        <v>1.292068017147856</v>
+        <v>1.31514066031121</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04720520727385038</v>
+        <v>0.04613236165399014</v>
       </c>
       <c r="W45">
-        <v>0.2246690121248261</v>
+        <v>0.2249219891219891</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1627765768063807</v>
+        <v>0.1590771091516902</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2450344993351626</v>
+        <v>0.2469344993351626</v>
       </c>
       <c r="C46">
-        <v>0.2241977582820919</v>
+        <v>0.2065790855037757</v>
       </c>
       <c r="D46">
-        <v>0.6678377582820919</v>
+        <v>0.6615290855037756</v>
       </c>
       <c r="E46">
-        <v>0.4666400000000001</v>
+        <v>0.47795</v>
       </c>
       <c r="F46">
-        <v>0.49764</v>
+        <v>0.50895</v>
       </c>
       <c r="G46">
         <v>0.054</v>
@@ -5053,37 +5053,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M46">
-        <v>0.117343512</v>
+        <v>0.12001041</v>
       </c>
       <c r="N46">
-        <v>-0.09867684533333335</v>
+        <v>-0.1013437433333333</v>
       </c>
       <c r="O46">
-        <v>-0.02861628514666667</v>
+        <v>-0.02938968556666667</v>
       </c>
       <c r="P46">
-        <v>-0.07006056018666668</v>
+        <v>-0.07195405776666668</v>
       </c>
       <c r="Q46">
-        <v>-0.06606056018666667</v>
+        <v>-0.06795405776666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2608371859312275</v>
+        <v>0.2647469529481589</v>
       </c>
       <c r="T46">
-        <v>1.31514066031121</v>
+        <v>1.339052308680505</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04613236165399014</v>
+        <v>0.04510719806167925</v>
       </c>
       <c r="W46">
-        <v>0.2249219891219891</v>
+        <v>0.225163722697056</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1590771091516902</v>
+        <v>0.1555420622816526</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2469344993351626</v>
+        <v>0.2488344993351627</v>
       </c>
       <c r="C47">
-        <v>0.2065790855037757</v>
+        <v>0.1890784860412561</v>
       </c>
       <c r="D47">
-        <v>0.6615290855037756</v>
+        <v>0.6553384860412561</v>
       </c>
       <c r="E47">
-        <v>0.47795</v>
+        <v>0.48926</v>
       </c>
       <c r="F47">
-        <v>0.50895</v>
+        <v>0.5202600000000001</v>
       </c>
       <c r="G47">
         <v>0.054</v>
@@ -5135,37 +5135,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M47">
-        <v>0.12001041</v>
+        <v>0.122677308</v>
       </c>
       <c r="N47">
-        <v>-0.1013437433333333</v>
+        <v>-0.1040106413333333</v>
       </c>
       <c r="O47">
-        <v>-0.02938968556666667</v>
+        <v>-0.03016308598666667</v>
       </c>
       <c r="P47">
-        <v>-0.07195405776666668</v>
+        <v>-0.07384755534666668</v>
       </c>
       <c r="Q47">
-        <v>-0.06795405776666667</v>
+        <v>-0.06984755534666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2647469529481589</v>
+        <v>0.2688015261509027</v>
       </c>
       <c r="T47">
-        <v>1.339052308680505</v>
+        <v>1.36384957365607</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04510719806167925</v>
+        <v>0.04412660679946883</v>
       </c>
       <c r="W47">
-        <v>0.225163722697056</v>
+        <v>0.2253949461166853</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1555420622816526</v>
+        <v>0.1521607131016167</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2488344993351627</v>
+        <v>0.2507344993351627</v>
       </c>
       <c r="C48">
-        <v>0.1890784860412561</v>
+        <v>0.1716926758310777</v>
       </c>
       <c r="D48">
-        <v>0.6553384860412561</v>
+        <v>0.6492626758310777</v>
       </c>
       <c r="E48">
-        <v>0.48926</v>
+        <v>0.50057</v>
       </c>
       <c r="F48">
-        <v>0.5202600000000001</v>
+        <v>0.53157</v>
       </c>
       <c r="G48">
         <v>0.054</v>
@@ -5217,37 +5217,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M48">
-        <v>0.122677308</v>
+        <v>0.125344206</v>
       </c>
       <c r="N48">
-        <v>-0.1040106413333333</v>
+        <v>-0.1066775393333333</v>
       </c>
       <c r="O48">
-        <v>-0.03016308598666667</v>
+        <v>-0.03093648640666667</v>
       </c>
       <c r="P48">
-        <v>-0.07384755534666668</v>
+        <v>-0.07574105292666668</v>
       </c>
       <c r="Q48">
-        <v>-0.06984755534666667</v>
+        <v>-0.07174105292666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2688015261509027</v>
+        <v>0.273009102116014</v>
       </c>
       <c r="T48">
-        <v>1.36384957365607</v>
+        <v>1.389582584479769</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04412660679946883</v>
+        <v>0.04318774282501205</v>
       </c>
       <c r="W48">
-        <v>0.2253949461166853</v>
+        <v>0.2256163302418622</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1521607131016167</v>
+        <v>0.1489232511207312</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2507344993351627</v>
+        <v>0.2526344993351627</v>
       </c>
       <c r="C49">
-        <v>0.1716926758310777</v>
+        <v>0.154418491480574</v>
       </c>
       <c r="D49">
-        <v>0.6492626758310777</v>
+        <v>0.6432984914805739</v>
       </c>
       <c r="E49">
-        <v>0.50057</v>
+        <v>0.51188</v>
       </c>
       <c r="F49">
-        <v>0.53157</v>
+        <v>0.54288</v>
       </c>
       <c r="G49">
         <v>0.054</v>
@@ -5299,37 +5299,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M49">
-        <v>0.125344206</v>
+        <v>0.128011104</v>
       </c>
       <c r="N49">
-        <v>-0.1066775393333333</v>
+        <v>-0.1093444373333333</v>
       </c>
       <c r="O49">
-        <v>-0.03093648640666667</v>
+        <v>-0.03170988682666667</v>
       </c>
       <c r="P49">
-        <v>-0.07574105292666668</v>
+        <v>-0.07763455050666668</v>
       </c>
       <c r="Q49">
-        <v>-0.07174105292666667</v>
+        <v>-0.07363455050666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.273009102116014</v>
+        <v>0.2773785079259374</v>
       </c>
       <c r="T49">
-        <v>1.389582584479769</v>
+        <v>1.416305326488996</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04318774282501205</v>
+        <v>0.04228799818282429</v>
       </c>
       <c r="W49">
-        <v>0.2256163302418622</v>
+        <v>0.2258284900284901</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1489232511207312</v>
+        <v>0.1458206833890493</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2526344993351627</v>
+        <v>0.2545344993351626</v>
       </c>
       <c r="C50">
-        <v>0.154418491480574</v>
+        <v>0.1372528847758553</v>
       </c>
       <c r="D50">
-        <v>0.6432984914805739</v>
+        <v>0.6374428847758552</v>
       </c>
       <c r="E50">
-        <v>0.51188</v>
+        <v>0.5231899999999999</v>
       </c>
       <c r="F50">
-        <v>0.54288</v>
+        <v>0.55419</v>
       </c>
       <c r="G50">
         <v>0.054</v>
@@ -5381,37 +5381,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M50">
-        <v>0.128011104</v>
+        <v>0.130678002</v>
       </c>
       <c r="N50">
-        <v>-0.1093444373333333</v>
+        <v>-0.1120113353333333</v>
       </c>
       <c r="O50">
-        <v>-0.03170988682666667</v>
+        <v>-0.03248328724666666</v>
       </c>
       <c r="P50">
-        <v>-0.07763455050666668</v>
+        <v>-0.07952804808666666</v>
       </c>
       <c r="Q50">
-        <v>-0.07363455050666667</v>
+        <v>-0.07552804808666666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2773785079259374</v>
+        <v>0.2819192629833087</v>
       </c>
       <c r="T50">
-        <v>1.416305326488996</v>
+        <v>1.44407601916525</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04228799818282429</v>
+        <v>0.04142497781174626</v>
       </c>
       <c r="W50">
-        <v>0.2258284900284901</v>
+        <v>0.2260319902319902</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1458206833890493</v>
+        <v>0.1428447510749871</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2545344993351626</v>
+        <v>0.2564344993351627</v>
       </c>
       <c r="C51">
-        <v>0.1372528847758553</v>
+        <v>0.1201929174870355</v>
       </c>
       <c r="D51">
-        <v>0.6374428847758552</v>
+        <v>0.6316929174870355</v>
       </c>
       <c r="E51">
-        <v>0.5231899999999999</v>
+        <v>0.5345</v>
       </c>
       <c r="F51">
-        <v>0.55419</v>
+        <v>0.5655</v>
       </c>
       <c r="G51">
         <v>0.054</v>
@@ -5463,37 +5463,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M51">
-        <v>0.130678002</v>
+        <v>0.1333449</v>
       </c>
       <c r="N51">
-        <v>-0.1120113353333333</v>
+        <v>-0.1146782333333334</v>
       </c>
       <c r="O51">
-        <v>-0.03248328724666666</v>
+        <v>-0.03325668766666667</v>
       </c>
       <c r="P51">
-        <v>-0.07952804808666666</v>
+        <v>-0.08142154566666668</v>
       </c>
       <c r="Q51">
-        <v>-0.07552804808666666</v>
+        <v>-0.07742154566666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2819192629833087</v>
+        <v>0.2866416482429748</v>
       </c>
       <c r="T51">
-        <v>1.44407601916525</v>
+        <v>1.472957539548555</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04142497781174626</v>
+        <v>0.04059647825551132</v>
       </c>
       <c r="W51">
-        <v>0.2260319902319902</v>
+        <v>0.2262273504273505</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1428447510749871</v>
+        <v>0.1399878560534873</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2564344993351627</v>
+        <v>0.2583344993351626</v>
       </c>
       <c r="C52">
-        <v>0.1201929174870355</v>
+        <v>0.1032357564520986</v>
       </c>
       <c r="D52">
-        <v>0.6316929174870355</v>
+        <v>0.6260457564520986</v>
       </c>
       <c r="E52">
-        <v>0.5345</v>
+        <v>0.54581</v>
       </c>
       <c r="F52">
-        <v>0.5655</v>
+        <v>0.57681</v>
       </c>
       <c r="G52">
         <v>0.054</v>
@@ -5545,37 +5545,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M52">
-        <v>0.1333449</v>
+        <v>0.136011798</v>
       </c>
       <c r="N52">
-        <v>-0.1146782333333334</v>
+        <v>-0.1173451313333334</v>
       </c>
       <c r="O52">
-        <v>-0.03325668766666667</v>
+        <v>-0.03403008808666667</v>
       </c>
       <c r="P52">
-        <v>-0.08142154566666668</v>
+        <v>-0.08331504324666669</v>
       </c>
       <c r="Q52">
-        <v>-0.07742154566666667</v>
+        <v>-0.07931504324666669</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2866416482429748</v>
+        <v>0.2915567839214029</v>
       </c>
       <c r="T52">
-        <v>1.472957539548555</v>
+        <v>1.503017897498526</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04059647825551132</v>
+        <v>0.03980046887795228</v>
       </c>
       <c r="W52">
-        <v>0.2262273504273505</v>
+        <v>0.2264150494385788</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1399878560534873</v>
+        <v>0.1372429961308699</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2583344993351626</v>
+        <v>0.2602344993351627</v>
       </c>
       <c r="C53">
-        <v>0.1032357564520986</v>
+        <v>0.08637866892212132</v>
       </c>
       <c r="D53">
-        <v>0.6260457564520986</v>
+        <v>0.6204986689221212</v>
       </c>
       <c r="E53">
-        <v>0.54581</v>
+        <v>0.5571199999999999</v>
       </c>
       <c r="F53">
-        <v>0.57681</v>
+        <v>0.58812</v>
       </c>
       <c r="G53">
         <v>0.054</v>
@@ -5627,37 +5627,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M53">
-        <v>0.136011798</v>
+        <v>0.138678696</v>
       </c>
       <c r="N53">
-        <v>-0.1173451313333334</v>
+        <v>-0.1200120293333333</v>
       </c>
       <c r="O53">
-        <v>-0.03403008808666667</v>
+        <v>-0.03480348850666666</v>
       </c>
       <c r="P53">
-        <v>-0.08331504324666669</v>
+        <v>-0.08520854082666666</v>
       </c>
       <c r="Q53">
-        <v>-0.07931504324666669</v>
+        <v>-0.08120854082666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2915567839214029</v>
+        <v>0.2966767169197655</v>
       </c>
       <c r="T53">
-        <v>1.503017897498526</v>
+        <v>1.534330770363079</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03980046887795228</v>
+        <v>0.03903507524568397</v>
       </c>
       <c r="W53">
-        <v>0.2264150494385788</v>
+        <v>0.2265955292570677</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1372429961308699</v>
+        <v>0.1346037077437379</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2602344993351627</v>
+        <v>0.2621344993351626</v>
       </c>
       <c r="C54">
-        <v>0.08637866892212132</v>
+        <v>0.06961901815178573</v>
       </c>
       <c r="D54">
-        <v>0.6204986689221212</v>
+        <v>0.6150490181517857</v>
       </c>
       <c r="E54">
-        <v>0.5571199999999999</v>
+        <v>0.56843</v>
       </c>
       <c r="F54">
-        <v>0.58812</v>
+        <v>0.59943</v>
       </c>
       <c r="G54">
         <v>0.054</v>
@@ -5709,37 +5709,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M54">
-        <v>0.138678696</v>
+        <v>0.141345594</v>
       </c>
       <c r="N54">
-        <v>-0.1200120293333333</v>
+        <v>-0.1226789273333334</v>
       </c>
       <c r="O54">
-        <v>-0.03480348850666666</v>
+        <v>-0.03557688892666667</v>
       </c>
       <c r="P54">
-        <v>-0.08520854082666666</v>
+        <v>-0.08710203840666669</v>
       </c>
       <c r="Q54">
-        <v>-0.08120854082666666</v>
+        <v>-0.08310203840666669</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2966767169197655</v>
+        <v>0.3020145194074201</v>
       </c>
       <c r="T54">
-        <v>1.534330770363079</v>
+        <v>1.566976105902719</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03903507524568397</v>
+        <v>0.03829856439199181</v>
       </c>
       <c r="W54">
-        <v>0.2265955292570677</v>
+        <v>0.2267691985163683</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1346037077437379</v>
+        <v>0.1320640151447994</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2621344993351626</v>
+        <v>0.2640344993351627</v>
       </c>
       <c r="C55">
-        <v>0.06961901815178573</v>
+        <v>0.05295425922023067</v>
       </c>
       <c r="D55">
-        <v>0.6150490181517857</v>
+        <v>0.6096942592202307</v>
       </c>
       <c r="E55">
-        <v>0.56843</v>
+        <v>0.57974</v>
       </c>
       <c r="F55">
-        <v>0.59943</v>
+        <v>0.6107400000000001</v>
       </c>
       <c r="G55">
         <v>0.054</v>
@@ -5791,37 +5791,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M55">
-        <v>0.141345594</v>
+        <v>0.144012492</v>
       </c>
       <c r="N55">
-        <v>-0.1226789273333334</v>
+        <v>-0.1253458253333334</v>
       </c>
       <c r="O55">
-        <v>-0.03557688892666667</v>
+        <v>-0.03635028934666667</v>
       </c>
       <c r="P55">
-        <v>-0.08710203840666669</v>
+        <v>-0.08899553598666668</v>
       </c>
       <c r="Q55">
-        <v>-0.08310203840666669</v>
+        <v>-0.08499553598666668</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3020145194074201</v>
+        <v>0.3075844002641031</v>
       </c>
       <c r="T55">
-        <v>1.566976105902719</v>
+        <v>1.601040803857126</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03829856439199181</v>
+        <v>0.03758933171806603</v>
       </c>
       <c r="W55">
-        <v>0.2267691985163683</v>
+        <v>0.2269364355808801</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1320640151447994</v>
+        <v>0.1296183852347105</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2640344993351627</v>
+        <v>0.2659344993351627</v>
       </c>
       <c r="C56">
-        <v>0.05295425922023067</v>
+        <v>0.03638193506832788</v>
       </c>
       <c r="D56">
-        <v>0.6096942592202307</v>
+        <v>0.6044319350683279</v>
       </c>
       <c r="E56">
-        <v>0.57974</v>
+        <v>0.5910500000000001</v>
       </c>
       <c r="F56">
-        <v>0.6107400000000001</v>
+        <v>0.6220500000000001</v>
       </c>
       <c r="G56">
         <v>0.054</v>
@@ -5873,37 +5873,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M56">
-        <v>0.144012492</v>
+        <v>0.14667939</v>
       </c>
       <c r="N56">
-        <v>-0.1253458253333334</v>
+        <v>-0.1280127233333334</v>
       </c>
       <c r="O56">
-        <v>-0.03635028934666667</v>
+        <v>-0.03712368976666667</v>
       </c>
       <c r="P56">
-        <v>-0.08899553598666668</v>
+        <v>-0.09088903356666669</v>
       </c>
       <c r="Q56">
-        <v>-0.08499553598666668</v>
+        <v>-0.08688903356666669</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3075844002641031</v>
+        <v>0.3134018313810832</v>
       </c>
       <c r="T56">
-        <v>1.601040803857126</v>
+        <v>1.636619488387284</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03758933171806603</v>
+        <v>0.03690588932319212</v>
       </c>
       <c r="W56">
-        <v>0.2269364355808801</v>
+        <v>0.2270975912975913</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1296183852347105</v>
+        <v>0.1272616873213521</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2659344993351627</v>
+        <v>0.2678344993351627</v>
       </c>
       <c r="C57">
-        <v>0.03638193506832788</v>
+        <v>0.01989967273941717</v>
       </c>
       <c r="D57">
-        <v>0.6044319350683279</v>
+        <v>0.5992596727394172</v>
       </c>
       <c r="E57">
-        <v>0.5910500000000001</v>
+        <v>0.60236</v>
       </c>
       <c r="F57">
-        <v>0.6220500000000001</v>
+        <v>0.63336</v>
       </c>
       <c r="G57">
         <v>0.054</v>
@@ -5955,37 +5955,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M57">
-        <v>0.14667939</v>
+        <v>0.149346288</v>
       </c>
       <c r="N57">
-        <v>-0.1280127233333334</v>
+        <v>-0.1306796213333334</v>
       </c>
       <c r="O57">
-        <v>-0.03712368976666667</v>
+        <v>-0.03789709018666667</v>
       </c>
       <c r="P57">
-        <v>-0.09088903356666669</v>
+        <v>-0.09278253114666668</v>
       </c>
       <c r="Q57">
-        <v>-0.08688903356666669</v>
+        <v>-0.08878253114666668</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3134018313810832</v>
+        <v>0.3194836911851988</v>
       </c>
       <c r="T57">
-        <v>1.636619488387284</v>
+        <v>1.673815385850631</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03690588932319212</v>
+        <v>0.03624685558527797</v>
       </c>
       <c r="W57">
-        <v>0.2270975912975913</v>
+        <v>0.2272529914529915</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1272616873213521</v>
+        <v>0.1249891571906137</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2678344993351627</v>
+        <v>0.2697344993351627</v>
       </c>
       <c r="C58">
-        <v>0.01989967273941717</v>
+        <v>0.003505179811416959</v>
       </c>
       <c r="D58">
-        <v>0.5992596727394172</v>
+        <v>0.594175179811417</v>
       </c>
       <c r="E58">
-        <v>0.60236</v>
+        <v>0.61367</v>
       </c>
       <c r="F58">
-        <v>0.63336</v>
+        <v>0.6446700000000001</v>
       </c>
       <c r="G58">
         <v>0.054</v>
@@ -6037,37 +6037,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M58">
-        <v>0.149346288</v>
+        <v>0.152013186</v>
       </c>
       <c r="N58">
-        <v>-0.1306796213333334</v>
+        <v>-0.1333465193333334</v>
       </c>
       <c r="O58">
-        <v>-0.03789709018666667</v>
+        <v>-0.03867049060666667</v>
       </c>
       <c r="P58">
-        <v>-0.09278253114666668</v>
+        <v>-0.09467602872666669</v>
       </c>
       <c r="Q58">
-        <v>-0.08878253114666668</v>
+        <v>-0.09067602872666669</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3194836911851988</v>
+        <v>0.3258484281895057</v>
       </c>
       <c r="T58">
-        <v>1.673815385850631</v>
+        <v>1.71274132505646</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03624685558527797</v>
+        <v>0.03561094583816782</v>
       </c>
       <c r="W58">
-        <v>0.2272529914529915</v>
+        <v>0.22740293897136</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1249891571906137</v>
+        <v>0.1227963649591994</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2697344993351627</v>
+        <v>0.2716344993351627</v>
       </c>
       <c r="C59">
-        <v>0.003505179811416959</v>
+        <v>-0.01280375899095909</v>
       </c>
       <c r="D59">
-        <v>0.594175179811417</v>
+        <v>0.589176241009041</v>
       </c>
       <c r="E59">
-        <v>0.61367</v>
+        <v>0.6249800000000001</v>
       </c>
       <c r="F59">
-        <v>0.6446700000000001</v>
+        <v>0.6559800000000001</v>
       </c>
       <c r="G59">
         <v>0.054</v>
@@ -6119,37 +6119,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M59">
-        <v>0.152013186</v>
+        <v>0.154680084</v>
       </c>
       <c r="N59">
-        <v>-0.1333465193333334</v>
+        <v>-0.1360134173333334</v>
       </c>
       <c r="O59">
-        <v>-0.03867049060666667</v>
+        <v>-0.03944389102666667</v>
       </c>
       <c r="P59">
-        <v>-0.09467602872666669</v>
+        <v>-0.09656952630666668</v>
       </c>
       <c r="Q59">
-        <v>-0.09067602872666669</v>
+        <v>-0.09256952630666668</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3258484281895057</v>
+        <v>0.3325162479083035</v>
       </c>
       <c r="T59">
-        <v>1.71274132505646</v>
+        <v>1.753520880414948</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03561094583816782</v>
+        <v>0.03499696401337183</v>
       </c>
       <c r="W59">
-        <v>0.22740293897136</v>
+        <v>0.2275477158856469</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1227963649591994</v>
+        <v>0.1206791862530063</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2716344993351626</v>
+        <v>0.2735344993351627</v>
       </c>
       <c r="C60">
-        <v>-0.01280375899095887</v>
+        <v>-0.02902928501439928</v>
       </c>
       <c r="D60">
-        <v>0.5891762410090411</v>
+        <v>0.5842607149856006</v>
       </c>
       <c r="E60">
-        <v>0.62498</v>
+        <v>0.6362899999999999</v>
       </c>
       <c r="F60">
-        <v>0.65598</v>
+        <v>0.6672899999999999</v>
       </c>
       <c r="G60">
         <v>0.054</v>
@@ -6201,37 +6201,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M60">
-        <v>0.154680084</v>
+        <v>0.157346982</v>
       </c>
       <c r="N60">
-        <v>-0.1360134173333333</v>
+        <v>-0.1386803153333333</v>
       </c>
       <c r="O60">
-        <v>-0.03944389102666666</v>
+        <v>-0.04021729144666666</v>
       </c>
       <c r="P60">
-        <v>-0.09656952630666667</v>
+        <v>-0.09846302388666667</v>
       </c>
       <c r="Q60">
-        <v>-0.09256952630666666</v>
+        <v>-0.09446302388666666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3325162479083034</v>
+        <v>0.3395093271255791</v>
       </c>
       <c r="T60">
-        <v>1.753520880414947</v>
+        <v>1.796289682376287</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03499696401337184</v>
+        <v>0.03440379513178926</v>
       </c>
       <c r="W60">
-        <v>0.2275477158856469</v>
+        <v>0.2276875851079241</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1206791862530063</v>
+        <v>0.1186337763165147</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2735344993351627</v>
+        <v>0.2754344993351626</v>
       </c>
       <c r="C61">
-        <v>-0.02902928501439928</v>
+        <v>-0.04517346873542805</v>
       </c>
       <c r="D61">
-        <v>0.5842607149856006</v>
+        <v>0.5794265312645719</v>
       </c>
       <c r="E61">
-        <v>0.6362899999999999</v>
+        <v>0.6476</v>
       </c>
       <c r="F61">
-        <v>0.6672899999999999</v>
+        <v>0.6786</v>
       </c>
       <c r="G61">
         <v>0.054</v>
@@ -6283,37 +6283,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M61">
-        <v>0.157346982</v>
+        <v>0.16001388</v>
       </c>
       <c r="N61">
-        <v>-0.1386803153333333</v>
+        <v>-0.1413472133333333</v>
       </c>
       <c r="O61">
-        <v>-0.04021729144666666</v>
+        <v>-0.04099069186666666</v>
       </c>
       <c r="P61">
-        <v>-0.09846302388666667</v>
+        <v>-0.1003565214666667</v>
       </c>
       <c r="Q61">
-        <v>-0.09446302388666666</v>
+        <v>-0.09635652146666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3395093271255791</v>
+        <v>0.3468520603037185</v>
       </c>
       <c r="T61">
-        <v>1.796289682376287</v>
+        <v>1.841196924435694</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03440379513178926</v>
+        <v>0.03383039854625944</v>
       </c>
       <c r="W61">
-        <v>0.2276875851079241</v>
+        <v>0.227822792022792</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1186337763165147</v>
+        <v>0.1166565467112395</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2754344993351626</v>
+        <v>0.2773344993351626</v>
       </c>
       <c r="C62">
-        <v>-0.04517346873542805</v>
+        <v>-0.06123831266824964</v>
       </c>
       <c r="D62">
-        <v>0.5794265312645719</v>
+        <v>0.5746716873317503</v>
       </c>
       <c r="E62">
-        <v>0.6476</v>
+        <v>0.65891</v>
       </c>
       <c r="F62">
-        <v>0.6786</v>
+        <v>0.68991</v>
       </c>
       <c r="G62">
         <v>0.054</v>
@@ -6365,37 +6365,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M62">
-        <v>0.16001388</v>
+        <v>0.162680778</v>
       </c>
       <c r="N62">
-        <v>-0.1413472133333333</v>
+        <v>-0.1440141113333334</v>
       </c>
       <c r="O62">
-        <v>-0.04099069186666666</v>
+        <v>-0.04176409228666667</v>
       </c>
       <c r="P62">
-        <v>-0.1003565214666667</v>
+        <v>-0.1022500190466667</v>
       </c>
       <c r="Q62">
-        <v>-0.09635652146666666</v>
+        <v>-0.09825001904666669</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3468520603037185</v>
+        <v>0.3545713439012498</v>
       </c>
       <c r="T62">
-        <v>1.841196924435694</v>
+        <v>1.888407101985328</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03383039854625944</v>
+        <v>0.03327580184877977</v>
       </c>
       <c r="W62">
-        <v>0.227822792022792</v>
+        <v>0.2279535659240577</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1166565467112395</v>
+        <v>0.1147441443061371</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2773344993351626</v>
+        <v>0.2792344993351626</v>
       </c>
       <c r="C63">
-        <v>-0.06123831266824964</v>
+        <v>-0.07722575413058719</v>
       </c>
       <c r="D63">
-        <v>0.5746716873317503</v>
+        <v>0.5699942458694127</v>
       </c>
       <c r="E63">
-        <v>0.65891</v>
+        <v>0.6702199999999999</v>
       </c>
       <c r="F63">
-        <v>0.68991</v>
+        <v>0.70122</v>
       </c>
       <c r="G63">
         <v>0.054</v>
@@ -6447,37 +6447,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M63">
-        <v>0.162680778</v>
+        <v>0.165347676</v>
       </c>
       <c r="N63">
-        <v>-0.1440141113333334</v>
+        <v>-0.1466810093333333</v>
       </c>
       <c r="O63">
-        <v>-0.04176409228666667</v>
+        <v>-0.04253749270666667</v>
       </c>
       <c r="P63">
-        <v>-0.1022500190466667</v>
+        <v>-0.1041435166266667</v>
       </c>
       <c r="Q63">
-        <v>-0.09825001904666669</v>
+        <v>-0.1001435166266667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3545713439012498</v>
+        <v>0.3626969055828617</v>
       </c>
       <c r="T63">
-        <v>1.888407101985328</v>
+        <v>1.938102025721783</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03327580184877977</v>
+        <v>0.03273909536734784</v>
       </c>
       <c r="W63">
-        <v>0.2279535659240577</v>
+        <v>0.2280801213123794</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1147441443061371</v>
+        <v>0.1128934323011995</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2792344993351626</v>
+        <v>0.2811344993351627</v>
       </c>
       <c r="C64">
-        <v>-0.07722575413058719</v>
+        <v>-0.09313766787553934</v>
       </c>
       <c r="D64">
-        <v>0.5699942458694127</v>
+        <v>0.5653923321244606</v>
       </c>
       <c r="E64">
-        <v>0.6702199999999999</v>
+        <v>0.68153</v>
       </c>
       <c r="F64">
-        <v>0.70122</v>
+        <v>0.71253</v>
       </c>
       <c r="G64">
         <v>0.054</v>
@@ -6529,37 +6529,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M64">
-        <v>0.165347676</v>
+        <v>0.168014574</v>
       </c>
       <c r="N64">
-        <v>-0.1466810093333333</v>
+        <v>-0.1493479073333333</v>
       </c>
       <c r="O64">
-        <v>-0.04253749270666667</v>
+        <v>-0.04331089312666667</v>
       </c>
       <c r="P64">
-        <v>-0.1041435166266667</v>
+        <v>-0.1060370142066667</v>
       </c>
       <c r="Q64">
-        <v>-0.1001435166266667</v>
+        <v>-0.1020370142066667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3626969055828617</v>
+        <v>0.3712616868148309</v>
       </c>
       <c r="T64">
-        <v>1.938102025721783</v>
+        <v>1.990483161552102</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03273909536734784</v>
+        <v>0.03221942718691376</v>
       </c>
       <c r="W64">
-        <v>0.2280801213123794</v>
+        <v>0.2282026590693257</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1128934323011995</v>
+        <v>0.1111014730583233</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2811344993351627</v>
+        <v>0.2830344993351627</v>
       </c>
       <c r="C65">
-        <v>-0.09313766787553934</v>
+        <v>-0.1089758685969648</v>
       </c>
       <c r="D65">
-        <v>0.5653923321244606</v>
+        <v>0.5608641314030351</v>
       </c>
       <c r="E65">
-        <v>0.68153</v>
+        <v>0.69284</v>
       </c>
       <c r="F65">
-        <v>0.71253</v>
+        <v>0.72384</v>
       </c>
       <c r="G65">
         <v>0.054</v>
@@ -6611,37 +6611,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M65">
-        <v>0.168014574</v>
+        <v>0.170681472</v>
       </c>
       <c r="N65">
-        <v>-0.1493479073333333</v>
+        <v>-0.1520148053333334</v>
       </c>
       <c r="O65">
-        <v>-0.04331089312666667</v>
+        <v>-0.04408429354666667</v>
       </c>
       <c r="P65">
-        <v>-0.1060370142066667</v>
+        <v>-0.1079305117866667</v>
       </c>
       <c r="Q65">
-        <v>-0.1020370142066667</v>
+        <v>-0.1039305117866667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3712616868148309</v>
+        <v>0.380302289226354</v>
       </c>
       <c r="T65">
-        <v>1.990483161552102</v>
+        <v>2.045774360484105</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03221942718691376</v>
+        <v>0.03171599863711822</v>
       </c>
       <c r="W65">
-        <v>0.2282026590693257</v>
+        <v>0.2283213675213675</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1111014730583233</v>
+        <v>0.1093655125417869</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2830344993351627</v>
+        <v>0.2849344993351627</v>
       </c>
       <c r="C66">
-        <v>-0.1089758685969648</v>
+        <v>-0.1247421133154327</v>
       </c>
       <c r="D66">
-        <v>0.5608641314030351</v>
+        <v>0.5564078866845673</v>
       </c>
       <c r="E66">
-        <v>0.69284</v>
+        <v>0.7041500000000001</v>
       </c>
       <c r="F66">
-        <v>0.72384</v>
+        <v>0.7351500000000001</v>
       </c>
       <c r="G66">
         <v>0.054</v>
@@ -6693,37 +6693,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M66">
-        <v>0.170681472</v>
+        <v>0.17334837</v>
       </c>
       <c r="N66">
-        <v>-0.1520148053333334</v>
+        <v>-0.1546817033333334</v>
       </c>
       <c r="O66">
-        <v>-0.04408429354666667</v>
+        <v>-0.04485769396666667</v>
       </c>
       <c r="P66">
-        <v>-0.1079305117866667</v>
+        <v>-0.1098240093666667</v>
       </c>
       <c r="Q66">
-        <v>-0.1039305117866667</v>
+        <v>-0.1058240093666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.380302289226354</v>
+        <v>0.3898594974899642</v>
       </c>
       <c r="T66">
-        <v>2.045774360484105</v>
+        <v>2.104225056497937</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03171599863711822</v>
+        <v>0.03122806019654717</v>
       </c>
       <c r="W66">
-        <v>0.2283213675213675</v>
+        <v>0.2284364234056542</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1093655125417869</v>
+        <v>0.1076829661949903</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2849344993351627</v>
+        <v>0.2868344993351627</v>
       </c>
       <c r="C67">
-        <v>-0.1247421133154327</v>
+        <v>-0.140438103651325</v>
       </c>
       <c r="D67">
-        <v>0.5564078866845673</v>
+        <v>0.5520218963486749</v>
       </c>
       <c r="E67">
-        <v>0.7041500000000001</v>
+        <v>0.71546</v>
       </c>
       <c r="F67">
-        <v>0.7351500000000001</v>
+        <v>0.74646</v>
       </c>
       <c r="G67">
         <v>0.054</v>
@@ -6775,37 +6775,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M67">
-        <v>0.17334837</v>
+        <v>0.176015268</v>
       </c>
       <c r="N67">
-        <v>-0.1546817033333334</v>
+        <v>-0.1573486013333333</v>
       </c>
       <c r="O67">
-        <v>-0.04485769396666667</v>
+        <v>-0.04563109438666667</v>
       </c>
       <c r="P67">
-        <v>-0.1098240093666667</v>
+        <v>-0.1117175069466667</v>
       </c>
       <c r="Q67">
-        <v>-0.1058240093666667</v>
+        <v>-0.1077175069466667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3898594974899642</v>
+        <v>0.3999788944749631</v>
       </c>
       <c r="T67">
-        <v>2.104225056497937</v>
+        <v>2.166114028747876</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03122806019654717</v>
+        <v>0.03075490776932676</v>
       </c>
       <c r="W67">
-        <v>0.2284364234056542</v>
+        <v>0.2285479927479928</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1076829661949903</v>
+        <v>0.1060514061011267</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2868344993351627</v>
+        <v>0.2887344993351627</v>
       </c>
       <c r="C68">
-        <v>-0.140438103651325</v>
+        <v>-0.156065487991272</v>
       </c>
       <c r="D68">
-        <v>0.5520218963486749</v>
+        <v>0.5477045120087281</v>
       </c>
       <c r="E68">
-        <v>0.71546</v>
+        <v>0.72677</v>
       </c>
       <c r="F68">
-        <v>0.74646</v>
+        <v>0.7577700000000001</v>
       </c>
       <c r="G68">
         <v>0.054</v>
@@ -6857,37 +6857,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M68">
-        <v>0.176015268</v>
+        <v>0.178682166</v>
       </c>
       <c r="N68">
-        <v>-0.1573486013333333</v>
+        <v>-0.1600154993333334</v>
       </c>
       <c r="O68">
-        <v>-0.04563109438666667</v>
+        <v>-0.04640449480666668</v>
       </c>
       <c r="P68">
-        <v>-0.1117175069466667</v>
+        <v>-0.1136110045266667</v>
       </c>
       <c r="Q68">
-        <v>-0.1077175069466667</v>
+        <v>-0.1096110045266667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3999788944749631</v>
+        <v>0.4107115882469317</v>
       </c>
       <c r="T68">
-        <v>2.166114028747876</v>
+        <v>2.231753847800842</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03075490776932676</v>
+        <v>0.0302958792951577</v>
       </c>
       <c r="W68">
-        <v>0.2285479927479928</v>
+        <v>0.2286562316622018</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1060514061011267</v>
+        <v>0.1044685492936472</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2887344993351627</v>
+        <v>0.2906344993351626</v>
       </c>
       <c r="C69">
-        <v>-0.156065487991272</v>
+        <v>-0.1716258635537127</v>
       </c>
       <c r="D69">
-        <v>0.5477045120087281</v>
+        <v>0.5434541364462874</v>
       </c>
       <c r="E69">
-        <v>0.72677</v>
+        <v>0.7380800000000001</v>
       </c>
       <c r="F69">
-        <v>0.7577700000000001</v>
+        <v>0.7690800000000001</v>
       </c>
       <c r="G69">
         <v>0.054</v>
@@ -6939,37 +6939,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M69">
-        <v>0.178682166</v>
+        <v>0.181349064</v>
       </c>
       <c r="N69">
-        <v>-0.1600154993333334</v>
+        <v>-0.1626823973333334</v>
       </c>
       <c r="O69">
-        <v>-0.04640449480666668</v>
+        <v>-0.04717789522666668</v>
       </c>
       <c r="P69">
-        <v>-0.1136110045266667</v>
+        <v>-0.1155045021066667</v>
       </c>
       <c r="Q69">
-        <v>-0.1096110045266667</v>
+        <v>-0.1115045021066667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4107115882469317</v>
+        <v>0.4221150753796483</v>
       </c>
       <c r="T69">
-        <v>2.231753847800842</v>
+        <v>2.301496155544618</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0302958792951577</v>
+        <v>0.0298503516584642</v>
       </c>
       <c r="W69">
-        <v>0.2286562316622018</v>
+        <v>0.2287612870789341</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1044685492936472</v>
+        <v>0.1029322470981524</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2906344993351626</v>
+        <v>0.2925344993351627</v>
       </c>
       <c r="C70">
-        <v>-0.1716258635537127</v>
+        <v>-0.1871207783590206</v>
       </c>
       <c r="D70">
-        <v>0.5434541364462874</v>
+        <v>0.5392692216409793</v>
       </c>
       <c r="E70">
-        <v>0.7380800000000001</v>
+        <v>0.74939</v>
       </c>
       <c r="F70">
-        <v>0.7690800000000001</v>
+        <v>0.78039</v>
       </c>
       <c r="G70">
         <v>0.054</v>
@@ -7021,37 +7021,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M70">
-        <v>0.181349064</v>
+        <v>0.184015962</v>
       </c>
       <c r="N70">
-        <v>-0.1626823973333334</v>
+        <v>-0.1653492953333333</v>
       </c>
       <c r="O70">
-        <v>-0.04717789522666668</v>
+        <v>-0.04795129564666666</v>
       </c>
       <c r="P70">
-        <v>-0.1155045021066667</v>
+        <v>-0.1173979996866667</v>
       </c>
       <c r="Q70">
-        <v>-0.1115045021066667</v>
+        <v>-0.1133979996866667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4221150753796483</v>
+        <v>0.434254271359637</v>
       </c>
       <c r="T70">
-        <v>2.301496155544618</v>
+        <v>2.3757379670138</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0298503516584642</v>
+        <v>0.02941773786631256</v>
       </c>
       <c r="W70">
-        <v>0.2287612870789341</v>
+        <v>0.2288632974111235</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1029322470981524</v>
+        <v>0.1014404754010778</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2925344993351627</v>
+        <v>0.2944344993351626</v>
       </c>
       <c r="C71">
-        <v>-0.1871207783590206</v>
+        <v>-0.2025517331092971</v>
       </c>
       <c r="D71">
-        <v>0.5392692216409793</v>
+        <v>0.5351482668907029</v>
       </c>
       <c r="E71">
-        <v>0.74939</v>
+        <v>0.7607</v>
       </c>
       <c r="F71">
-        <v>0.78039</v>
+        <v>0.7917000000000001</v>
       </c>
       <c r="G71">
         <v>0.054</v>
@@ -7103,37 +7103,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M71">
-        <v>0.184015962</v>
+        <v>0.18668286</v>
       </c>
       <c r="N71">
-        <v>-0.1653492953333333</v>
+        <v>-0.1680161933333334</v>
       </c>
       <c r="O71">
-        <v>-0.04795129564666666</v>
+        <v>-0.04872469606666668</v>
       </c>
       <c r="P71">
-        <v>-0.1173979996866667</v>
+        <v>-0.1192914972666667</v>
       </c>
       <c r="Q71">
-        <v>-0.1133979996866667</v>
+        <v>-0.1152914972666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.434254271359637</v>
+        <v>0.4472027470716249</v>
       </c>
       <c r="T71">
-        <v>2.3757379670138</v>
+        <v>2.454929232580926</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02941773786631256</v>
+        <v>0.02899748446822237</v>
       </c>
       <c r="W71">
-        <v>0.2288632974111235</v>
+        <v>0.2289623931623932</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1014404754010778</v>
+        <v>0.09999132575249092</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2944344993351626</v>
+        <v>0.2963344993351627</v>
       </c>
       <c r="C72">
-        <v>-0.2025517331092971</v>
+        <v>-0.2179201829826303</v>
       </c>
       <c r="D72">
-        <v>0.5351482668907029</v>
+        <v>0.5310898170173698</v>
       </c>
       <c r="E72">
-        <v>0.7607</v>
+        <v>0.7720100000000001</v>
       </c>
       <c r="F72">
-        <v>0.7917000000000001</v>
+        <v>0.8030100000000001</v>
       </c>
       <c r="G72">
         <v>0.054</v>
@@ -7185,37 +7185,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M72">
-        <v>0.18668286</v>
+        <v>0.189349758</v>
       </c>
       <c r="N72">
-        <v>-0.1680161933333334</v>
+        <v>-0.1706830913333334</v>
       </c>
       <c r="O72">
-        <v>-0.04872469606666668</v>
+        <v>-0.04949809648666667</v>
       </c>
       <c r="P72">
-        <v>-0.1192914972666667</v>
+        <v>-0.1211849948466667</v>
       </c>
       <c r="Q72">
-        <v>-0.1152914972666667</v>
+        <v>-0.1171849948466667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4472027470716249</v>
+        <v>0.4610442211085775</v>
       </c>
       <c r="T72">
-        <v>2.454929232580926</v>
+        <v>2.53958196473889</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02899748446822237</v>
+        <v>0.02858906919402206</v>
       </c>
       <c r="W72">
-        <v>0.2289623931623932</v>
+        <v>0.2290586974840496</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.09999132575249092</v>
+        <v>0.09858299722076569</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2963344993351626</v>
+        <v>0.2982344993351627</v>
       </c>
       <c r="C73">
-        <v>-0.2179201829826301</v>
+        <v>-0.2332275393463227</v>
       </c>
       <c r="D73">
-        <v>0.5310898170173699</v>
+        <v>0.5270924606536772</v>
       </c>
       <c r="E73">
-        <v>0.77201</v>
+        <v>0.7833199999999999</v>
       </c>
       <c r="F73">
-        <v>0.80301</v>
+        <v>0.8143199999999999</v>
       </c>
       <c r="G73">
         <v>0.054</v>
@@ -7267,37 +7267,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M73">
-        <v>0.189349758</v>
+        <v>0.192016656</v>
       </c>
       <c r="N73">
-        <v>-0.1706830913333333</v>
+        <v>-0.1733499893333333</v>
       </c>
       <c r="O73">
-        <v>-0.04949809648666666</v>
+        <v>-0.05027149690666666</v>
       </c>
       <c r="P73">
-        <v>-0.1211849948466667</v>
+        <v>-0.1230784924266667</v>
       </c>
       <c r="Q73">
-        <v>-0.1171849948466667</v>
+        <v>-0.1190784924266667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4610442211085773</v>
+        <v>0.4758743718624551</v>
       </c>
       <c r="T73">
-        <v>2.539581964738889</v>
+        <v>2.63028132062242</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02858906919402206</v>
+        <v>0.02819199878854953</v>
       </c>
       <c r="W73">
-        <v>0.2290586974840496</v>
+        <v>0.22915232668566</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.09858299722076569</v>
+        <v>0.09721378892603294</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2982344993351627</v>
+        <v>0.3001344993351627</v>
       </c>
       <c r="C74">
-        <v>-0.2332275393463227</v>
+        <v>-0.2484751713933313</v>
       </c>
       <c r="D74">
-        <v>0.5270924606536772</v>
+        <v>0.5231548286066686</v>
       </c>
       <c r="E74">
-        <v>0.7833199999999999</v>
+        <v>0.7946299999999999</v>
       </c>
       <c r="F74">
-        <v>0.8143199999999999</v>
+        <v>0.82563</v>
       </c>
       <c r="G74">
         <v>0.054</v>
@@ -7349,37 +7349,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M74">
-        <v>0.192016656</v>
+        <v>0.194683554</v>
       </c>
       <c r="N74">
-        <v>-0.1733499893333333</v>
+        <v>-0.1760168873333333</v>
       </c>
       <c r="O74">
-        <v>-0.05027149690666666</v>
+        <v>-0.05104489732666666</v>
       </c>
       <c r="P74">
-        <v>-0.1230784924266667</v>
+        <v>-0.1249719900066667</v>
       </c>
       <c r="Q74">
-        <v>-0.1190784924266667</v>
+        <v>-0.1209719900066667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4758743718624551</v>
+        <v>0.4918030523018053</v>
       </c>
       <c r="T74">
-        <v>2.63028132062242</v>
+        <v>2.72769914731214</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02819199878854953</v>
+        <v>0.02780580702432282</v>
       </c>
       <c r="W74">
-        <v>0.22915232668566</v>
+        <v>0.2292433907036647</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.09721378892603294</v>
+        <v>0.09588209318732011</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3001344993351627</v>
+        <v>0.3020344993351626</v>
       </c>
       <c r="C75">
-        <v>-0.2484751713933313</v>
+        <v>-0.2636644077058954</v>
       </c>
       <c r="D75">
-        <v>0.5231548286066686</v>
+        <v>0.5192755922941046</v>
       </c>
       <c r="E75">
-        <v>0.7946299999999999</v>
+        <v>0.80594</v>
       </c>
       <c r="F75">
-        <v>0.82563</v>
+        <v>0.83694</v>
       </c>
       <c r="G75">
         <v>0.054</v>
@@ -7431,37 +7431,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M75">
-        <v>0.194683554</v>
+        <v>0.197350452</v>
       </c>
       <c r="N75">
-        <v>-0.1760168873333333</v>
+        <v>-0.1786837853333333</v>
       </c>
       <c r="O75">
-        <v>-0.05104489732666666</v>
+        <v>-0.05181829774666667</v>
       </c>
       <c r="P75">
-        <v>-0.1249719900066667</v>
+        <v>-0.1268654875866667</v>
       </c>
       <c r="Q75">
-        <v>-0.1209719900066667</v>
+        <v>-0.1228654875866667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4918030523018053</v>
+        <v>0.5089570158518747</v>
       </c>
       <c r="T75">
-        <v>2.72769914731214</v>
+        <v>2.832610652977991</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02780580702432282</v>
+        <v>0.02743005287534549</v>
       </c>
       <c r="W75">
-        <v>0.2292433907036647</v>
+        <v>0.2293319935319935</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09588209318732011</v>
+        <v>0.09458638922532925</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3020344993351626</v>
+        <v>0.3039344993351626</v>
       </c>
       <c r="C76">
-        <v>-0.2636644077058954</v>
+        <v>-0.278796537750116</v>
       </c>
       <c r="D76">
-        <v>0.5192755922941046</v>
+        <v>0.5154534622498839</v>
       </c>
       <c r="E76">
-        <v>0.80594</v>
+        <v>0.8172499999999999</v>
       </c>
       <c r="F76">
-        <v>0.83694</v>
+        <v>0.8482499999999999</v>
       </c>
       <c r="G76">
         <v>0.054</v>
@@ -7513,37 +7513,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M76">
-        <v>0.197350452</v>
+        <v>0.20001735</v>
       </c>
       <c r="N76">
-        <v>-0.1786837853333333</v>
+        <v>-0.1813506833333333</v>
       </c>
       <c r="O76">
-        <v>-0.05181829774666667</v>
+        <v>-0.05259169816666666</v>
       </c>
       <c r="P76">
-        <v>-0.1268654875866667</v>
+        <v>-0.1287589851666667</v>
       </c>
       <c r="Q76">
-        <v>-0.1228654875866667</v>
+        <v>-0.1247589851666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5089570158518747</v>
+        <v>0.5274832964859497</v>
       </c>
       <c r="T76">
-        <v>2.832610652977991</v>
+        <v>2.945915079097111</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02743005287534549</v>
+        <v>0.02706431883700755</v>
       </c>
       <c r="W76">
-        <v>0.2293319935319935</v>
+        <v>0.2294182336182336</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09458638922532925</v>
+        <v>0.09332523736899156</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3039344993351626</v>
+        <v>0.3058344993351627</v>
       </c>
       <c r="C77">
-        <v>-0.278796537750116</v>
+        <v>-0.2938728133050088</v>
       </c>
       <c r="D77">
-        <v>0.5154534622498839</v>
+        <v>0.5116871866949911</v>
       </c>
       <c r="E77">
-        <v>0.8172499999999999</v>
+        <v>0.82856</v>
       </c>
       <c r="F77">
-        <v>0.8482499999999999</v>
+        <v>0.85956</v>
       </c>
       <c r="G77">
         <v>0.054</v>
@@ -7595,37 +7595,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M77">
-        <v>0.20001735</v>
+        <v>0.202684248</v>
       </c>
       <c r="N77">
-        <v>-0.1813506833333333</v>
+        <v>-0.1840175813333333</v>
       </c>
       <c r="O77">
-        <v>-0.05259169816666666</v>
+        <v>-0.05336509858666667</v>
       </c>
       <c r="P77">
-        <v>-0.1287589851666667</v>
+        <v>-0.1306524827466667</v>
       </c>
       <c r="Q77">
-        <v>-0.1247589851666667</v>
+        <v>-0.1266524827466667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5274832964859497</v>
+        <v>0.547553433839531</v>
       </c>
       <c r="T77">
-        <v>2.945915079097111</v>
+        <v>3.068661540726158</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02706431883700755</v>
+        <v>0.02670820937862587</v>
       </c>
       <c r="W77">
-        <v>0.2294182336182336</v>
+        <v>0.22950220422852</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.09332523736899156</v>
+        <v>0.09209727371939957</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3058344993351627</v>
+        <v>0.3077344993351626</v>
       </c>
       <c r="C78">
-        <v>-0.2938728133050088</v>
+        <v>-0.3088944498293617</v>
       </c>
       <c r="D78">
-        <v>0.5116871866949911</v>
+        <v>0.5079755501706383</v>
       </c>
       <c r="E78">
-        <v>0.82856</v>
+        <v>0.83987</v>
       </c>
       <c r="F78">
-        <v>0.85956</v>
+        <v>0.87087</v>
       </c>
       <c r="G78">
         <v>0.054</v>
@@ -7677,37 +7677,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M78">
-        <v>0.202684248</v>
+        <v>0.205351146</v>
       </c>
       <c r="N78">
-        <v>-0.1840175813333333</v>
+        <v>-0.1866844793333333</v>
       </c>
       <c r="O78">
-        <v>-0.05336509858666667</v>
+        <v>-0.05413849900666667</v>
       </c>
       <c r="P78">
-        <v>-0.1306524827466667</v>
+        <v>-0.1325459803266667</v>
       </c>
       <c r="Q78">
-        <v>-0.1266524827466667</v>
+        <v>-0.1285459803266667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.547553433839531</v>
+        <v>0.5693688005282062</v>
       </c>
       <c r="T78">
-        <v>3.068661540726158</v>
+        <v>3.202081607714251</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02670820937862587</v>
+        <v>0.0263613495165658</v>
       </c>
       <c r="W78">
-        <v>0.22950220422852</v>
+        <v>0.2295839937839938</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09209727371939957</v>
+        <v>0.09090120522953726</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3077344993351626</v>
+        <v>0.3096344993351626</v>
       </c>
       <c r="C79">
-        <v>-0.3088944498293617</v>
+        <v>-0.3238626277695337</v>
       </c>
       <c r="D79">
-        <v>0.5079755501706383</v>
+        <v>0.5043173722304664</v>
       </c>
       <c r="E79">
-        <v>0.83987</v>
+        <v>0.85118</v>
       </c>
       <c r="F79">
-        <v>0.87087</v>
+        <v>0.8821800000000001</v>
       </c>
       <c r="G79">
         <v>0.054</v>
@@ -7759,37 +7759,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M79">
-        <v>0.205351146</v>
+        <v>0.208018044</v>
       </c>
       <c r="N79">
-        <v>-0.1866844793333333</v>
+        <v>-0.1893513773333333</v>
       </c>
       <c r="O79">
-        <v>-0.05413849900666667</v>
+        <v>-0.05491189942666667</v>
       </c>
       <c r="P79">
-        <v>-0.1325459803266667</v>
+        <v>-0.1344394779066667</v>
       </c>
       <c r="Q79">
-        <v>-0.1285459803266667</v>
+        <v>-0.1304394779066667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5693688005282062</v>
+        <v>0.5931673823703975</v>
       </c>
       <c r="T79">
-        <v>3.202081607714251</v>
+        <v>3.347630771701263</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0263613495165658</v>
+        <v>0.02602338349712265</v>
       </c>
       <c r="W79">
-        <v>0.2295839937839938</v>
+        <v>0.2296636861713785</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.09090120522953726</v>
+        <v>0.08973580516249191</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3096344993351626</v>
+        <v>0.3115344993351626</v>
       </c>
       <c r="C80">
-        <v>-0.3238626277695337</v>
+        <v>-0.3387784938111474</v>
       </c>
       <c r="D80">
-        <v>0.5043173722304664</v>
+        <v>0.5007115061888525</v>
       </c>
       <c r="E80">
-        <v>0.85118</v>
+        <v>0.86249</v>
       </c>
       <c r="F80">
-        <v>0.8821800000000001</v>
+        <v>0.89349</v>
       </c>
       <c r="G80">
         <v>0.054</v>
@@ -7841,37 +7841,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M80">
-        <v>0.208018044</v>
+        <v>0.210684942</v>
       </c>
       <c r="N80">
-        <v>-0.1893513773333333</v>
+        <v>-0.1920182753333333</v>
       </c>
       <c r="O80">
-        <v>-0.05491189942666667</v>
+        <v>-0.05568529984666667</v>
       </c>
       <c r="P80">
-        <v>-0.1344394779066667</v>
+        <v>-0.1363329754866667</v>
       </c>
       <c r="Q80">
-        <v>-0.1304394779066667</v>
+        <v>-0.1323329754866667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5931673823703975</v>
+        <v>0.6192324958166069</v>
       </c>
       <c r="T80">
-        <v>3.347630771701263</v>
+        <v>3.507041760829895</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02602338349712265</v>
+        <v>0.02569397357943755</v>
       </c>
       <c r="W80">
-        <v>0.2296636861713785</v>
+        <v>0.2297413610299686</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.08973580516249191</v>
+        <v>0.08859990889461222</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3115344993351626</v>
+        <v>0.3134344993351627</v>
       </c>
       <c r="C81">
-        <v>-0.3387784938111474</v>
+        <v>-0.3536431620774663</v>
       </c>
       <c r="D81">
-        <v>0.5007115061888525</v>
+        <v>0.4971568379225337</v>
       </c>
       <c r="E81">
-        <v>0.86249</v>
+        <v>0.8738</v>
       </c>
       <c r="F81">
-        <v>0.89349</v>
+        <v>0.9048</v>
       </c>
       <c r="G81">
         <v>0.054</v>
@@ -7923,37 +7923,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M81">
-        <v>0.210684942</v>
+        <v>0.21335184</v>
       </c>
       <c r="N81">
-        <v>-0.1920182753333333</v>
+        <v>-0.1946851733333334</v>
       </c>
       <c r="O81">
-        <v>-0.05568529984666667</v>
+        <v>-0.05645870026666667</v>
       </c>
       <c r="P81">
-        <v>-0.1363329754866667</v>
+        <v>-0.1382264730666667</v>
       </c>
       <c r="Q81">
-        <v>-0.1323329754866667</v>
+        <v>-0.1342264730666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6192324958166069</v>
+        <v>0.6479041206074372</v>
       </c>
       <c r="T81">
-        <v>3.507041760829895</v>
+        <v>3.682393848871389</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02569397357943755</v>
+        <v>0.02537279890969458</v>
       </c>
       <c r="W81">
-        <v>0.2297413610299686</v>
+        <v>0.229817094017094</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08859990889461222</v>
+        <v>0.08749241003342956</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3134344993351627</v>
+        <v>0.3153344993351627</v>
       </c>
       <c r="C82">
-        <v>-0.3536431620774663</v>
+        <v>-0.3684577152770855</v>
       </c>
       <c r="D82">
-        <v>0.4971568379225337</v>
+        <v>0.4936522847229146</v>
       </c>
       <c r="E82">
-        <v>0.8738</v>
+        <v>0.8851100000000001</v>
       </c>
       <c r="F82">
-        <v>0.9048</v>
+        <v>0.9161100000000001</v>
       </c>
       <c r="G82">
         <v>0.054</v>
@@ -8005,37 +8005,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M82">
-        <v>0.21335184</v>
+        <v>0.216018738</v>
       </c>
       <c r="N82">
-        <v>-0.1946851733333334</v>
+        <v>-0.1973520713333334</v>
       </c>
       <c r="O82">
-        <v>-0.05645870026666667</v>
+        <v>-0.05723210068666668</v>
       </c>
       <c r="P82">
-        <v>-0.1382264730666667</v>
+        <v>-0.1401199706466667</v>
       </c>
       <c r="Q82">
-        <v>-0.1342264730666667</v>
+        <v>-0.1361199706466667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6479041206074372</v>
+        <v>0.6795938111657235</v>
       </c>
       <c r="T82">
-        <v>3.682393848871389</v>
+        <v>3.876204051443568</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02537279890969458</v>
+        <v>0.02505955447871069</v>
       </c>
       <c r="W82">
-        <v>0.229817094017094</v>
+        <v>0.22989095705392</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.08749241003342956</v>
+        <v>0.08641225682314035</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3153344993351627</v>
+        <v>0.3172344993351627</v>
       </c>
       <c r="C83">
-        <v>-0.3684577152770855</v>
+        <v>-0.3832232058034221</v>
       </c>
       <c r="D83">
-        <v>0.4936522847229146</v>
+        <v>0.490196794196578</v>
       </c>
       <c r="E83">
-        <v>0.8851100000000001</v>
+        <v>0.89642</v>
       </c>
       <c r="F83">
-        <v>0.9161100000000001</v>
+        <v>0.92742</v>
       </c>
       <c r="G83">
         <v>0.054</v>
@@ -8087,37 +8087,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M83">
-        <v>0.216018738</v>
+        <v>0.218685636</v>
       </c>
       <c r="N83">
-        <v>-0.1973520713333334</v>
+        <v>-0.2000189693333334</v>
       </c>
       <c r="O83">
-        <v>-0.05723210068666668</v>
+        <v>-0.05800550110666667</v>
       </c>
       <c r="P83">
-        <v>-0.1401199706466667</v>
+        <v>-0.1420134682266667</v>
       </c>
       <c r="Q83">
-        <v>-0.1361199706466667</v>
+        <v>-0.1380134682266667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6795938111657235</v>
+        <v>0.7148045784527081</v>
       </c>
       <c r="T83">
-        <v>3.876204051443568</v>
+        <v>4.091548720968211</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02505955447871069</v>
+        <v>0.02475395015579959</v>
       </c>
       <c r="W83">
-        <v>0.22989095705392</v>
+        <v>0.2299630185532625</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08641225682314035</v>
+        <v>0.08535844881310206</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3172344993351627</v>
+        <v>0.3191344993351626</v>
       </c>
       <c r="C84">
-        <v>-0.3832232058034221</v>
+        <v>-0.3979406567883467</v>
       </c>
       <c r="D84">
-        <v>0.490196794196578</v>
+        <v>0.4867893432116533</v>
       </c>
       <c r="E84">
-        <v>0.89642</v>
+        <v>0.90773</v>
       </c>
       <c r="F84">
-        <v>0.92742</v>
+        <v>0.9387300000000001</v>
       </c>
       <c r="G84">
         <v>0.054</v>
@@ -8169,37 +8169,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M84">
-        <v>0.218685636</v>
+        <v>0.221352534</v>
       </c>
       <c r="N84">
-        <v>-0.2000189693333334</v>
+        <v>-0.2026858673333334</v>
       </c>
       <c r="O84">
-        <v>-0.05800550110666667</v>
+        <v>-0.05877890152666667</v>
       </c>
       <c r="P84">
-        <v>-0.1420134682266667</v>
+        <v>-0.1439069658066667</v>
       </c>
       <c r="Q84">
-        <v>-0.1380134682266667</v>
+        <v>-0.1399069658066667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7148045784527081</v>
+        <v>0.7541577889499262</v>
       </c>
       <c r="T84">
-        <v>4.091548720968211</v>
+        <v>4.332228057495753</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02475395015579959</v>
+        <v>0.0244557097924767</v>
       </c>
       <c r="W84">
-        <v>0.2299630185532625</v>
+        <v>0.230033343630934</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08535844881310206</v>
+        <v>0.08433003376716108</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3191344993351626</v>
+        <v>0.3210344993351627</v>
       </c>
       <c r="C85">
-        <v>-0.3979406567883467</v>
+        <v>-0.4126110631121771</v>
       </c>
       <c r="D85">
-        <v>0.4867893432116533</v>
+        <v>0.483428936887823</v>
       </c>
       <c r="E85">
-        <v>0.90773</v>
+        <v>0.9190400000000001</v>
       </c>
       <c r="F85">
-        <v>0.9387300000000001</v>
+        <v>0.9500400000000001</v>
       </c>
       <c r="G85">
         <v>0.054</v>
@@ -8251,37 +8251,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M85">
-        <v>0.221352534</v>
+        <v>0.224019432</v>
       </c>
       <c r="N85">
-        <v>-0.2026858673333334</v>
+        <v>-0.2053527653333334</v>
       </c>
       <c r="O85">
-        <v>-0.05877890152666667</v>
+        <v>-0.05955230194666668</v>
       </c>
       <c r="P85">
-        <v>-0.1439069658066667</v>
+        <v>-0.1458004633866667</v>
       </c>
       <c r="Q85">
-        <v>-0.1399069658066667</v>
+        <v>-0.1418004633866667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7541577889499262</v>
+        <v>0.7984301507592968</v>
       </c>
       <c r="T85">
-        <v>4.332228057495753</v>
+        <v>4.602992311089238</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0244557097924767</v>
+        <v>0.02416457039018531</v>
       </c>
       <c r="W85">
-        <v>0.230033343630934</v>
+        <v>0.2301019943019943</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08433003376716108</v>
+        <v>0.08332610479374247</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3210344993351626</v>
+        <v>0.3229344993351627</v>
       </c>
       <c r="C86">
-        <v>-0.4126110631121769</v>
+        <v>-0.4272353923721224</v>
       </c>
       <c r="D86">
-        <v>0.4834289368878231</v>
+        <v>0.4801146076278776</v>
       </c>
       <c r="E86">
-        <v>0.91904</v>
+        <v>0.9303499999999999</v>
       </c>
       <c r="F86">
-        <v>0.95004</v>
+        <v>0.9613499999999999</v>
       </c>
       <c r="G86">
         <v>0.054</v>
@@ -8333,37 +8333,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M86">
-        <v>0.224019432</v>
+        <v>0.22668633</v>
       </c>
       <c r="N86">
-        <v>-0.2053527653333334</v>
+        <v>-0.2080196633333333</v>
       </c>
       <c r="O86">
-        <v>-0.05955230194666667</v>
+        <v>-0.06032570236666666</v>
       </c>
       <c r="P86">
-        <v>-0.1458004633866667</v>
+        <v>-0.1476939609666667</v>
       </c>
       <c r="Q86">
-        <v>-0.1418004633866667</v>
+        <v>-0.1436939609666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7984301507592962</v>
+        <v>0.8486054941432496</v>
       </c>
       <c r="T86">
-        <v>4.602992311089235</v>
+        <v>4.909858465161852</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02416457039018531</v>
+        <v>0.02388028132677137</v>
       </c>
       <c r="W86">
-        <v>0.2301019943019943</v>
+        <v>0.2301690296631473</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08332610479374247</v>
+        <v>0.08234579767852201</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3229344993351627</v>
+        <v>0.3248344993351626</v>
       </c>
       <c r="C87">
-        <v>-0.4272353923721224</v>
+        <v>-0.4418145858111646</v>
       </c>
       <c r="D87">
-        <v>0.4801146076278776</v>
+        <v>0.4768454141888353</v>
       </c>
       <c r="E87">
-        <v>0.9303499999999999</v>
+        <v>0.9416599999999999</v>
       </c>
       <c r="F87">
-        <v>0.9613499999999999</v>
+        <v>0.97266</v>
       </c>
       <c r="G87">
         <v>0.054</v>
@@ -8415,37 +8415,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M87">
-        <v>0.22668633</v>
+        <v>0.229353228</v>
       </c>
       <c r="N87">
-        <v>-0.2080196633333333</v>
+        <v>-0.2106865613333333</v>
       </c>
       <c r="O87">
-        <v>-0.06032570236666666</v>
+        <v>-0.06109910278666666</v>
       </c>
       <c r="P87">
-        <v>-0.1476939609666667</v>
+        <v>-0.1495874585466667</v>
       </c>
       <c r="Q87">
-        <v>-0.1436939609666667</v>
+        <v>-0.1455874585466667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8486054941432496</v>
+        <v>0.9059487437249101</v>
       </c>
       <c r="T87">
-        <v>4.909858465161852</v>
+        <v>5.260562641244841</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02388028132677137</v>
+        <v>0.02360260363692519</v>
       </c>
       <c r="W87">
-        <v>0.2301690296631473</v>
+        <v>0.2302345060624131</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08234579767852201</v>
+        <v>0.08138828840319035</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3248344993351626</v>
+        <v>0.3267344993351626</v>
       </c>
       <c r="C88">
-        <v>-0.4418145858111646</v>
+        <v>-0.4563495592092445</v>
       </c>
       <c r="D88">
-        <v>0.4768454141888353</v>
+        <v>0.4736204407907555</v>
       </c>
       <c r="E88">
-        <v>0.9416599999999999</v>
+        <v>0.95297</v>
       </c>
       <c r="F88">
-        <v>0.97266</v>
+        <v>0.98397</v>
       </c>
       <c r="G88">
         <v>0.054</v>
@@ -8497,37 +8497,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M88">
-        <v>0.229353228</v>
+        <v>0.232020126</v>
       </c>
       <c r="N88">
-        <v>-0.2106865613333333</v>
+        <v>-0.2133534593333334</v>
       </c>
       <c r="O88">
-        <v>-0.06109910278666666</v>
+        <v>-0.06187250320666667</v>
       </c>
       <c r="P88">
-        <v>-0.1495874585466667</v>
+        <v>-0.1514809561266667</v>
       </c>
       <c r="Q88">
-        <v>-0.1455874585466667</v>
+        <v>-0.1474809561266667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9059487437249101</v>
+        <v>0.9721140317037493</v>
       </c>
       <c r="T88">
-        <v>5.260562641244841</v>
+        <v>5.665221305955982</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02360260363692519</v>
+        <v>0.02333130934224789</v>
       </c>
       <c r="W88">
-        <v>0.2302345060624131</v>
+        <v>0.230298477257098</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08138828840319035</v>
+        <v>0.08045279083533752</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3267344993351626</v>
+        <v>0.3286344993351626</v>
       </c>
       <c r="C89">
-        <v>-0.4563495592092445</v>
+        <v>-0.4708412037385283</v>
       </c>
       <c r="D89">
-        <v>0.4736204407907555</v>
+        <v>0.4704387962614717</v>
       </c>
       <c r="E89">
-        <v>0.95297</v>
+        <v>0.96428</v>
       </c>
       <c r="F89">
-        <v>0.98397</v>
+        <v>0.9952800000000001</v>
       </c>
       <c r="G89">
         <v>0.054</v>
@@ -8579,37 +8579,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M89">
-        <v>0.232020126</v>
+        <v>0.234687024</v>
       </c>
       <c r="N89">
-        <v>-0.2133534593333334</v>
+        <v>-0.2160203573333334</v>
       </c>
       <c r="O89">
-        <v>-0.06187250320666667</v>
+        <v>-0.06264590362666667</v>
       </c>
       <c r="P89">
-        <v>-0.1514809561266667</v>
+        <v>-0.1533744537066667</v>
       </c>
       <c r="Q89">
-        <v>-0.1474809561266667</v>
+        <v>-0.1493744537066667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9721140317037493</v>
+        <v>1.049306867679062</v>
       </c>
       <c r="T89">
-        <v>5.665221305955982</v>
+        <v>6.137323081452315</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02333130934224789</v>
+        <v>0.02306618082699507</v>
       </c>
       <c r="W89">
-        <v>0.230298477257098</v>
+        <v>0.2303609945609946</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08045279083533752</v>
+        <v>0.07953855457584502</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3286344993351626</v>
+        <v>0.3305344993351627</v>
       </c>
       <c r="C90">
-        <v>-0.4708412037385283</v>
+        <v>-0.485290386784432</v>
       </c>
       <c r="D90">
-        <v>0.4704387962614717</v>
+        <v>0.467299613215568</v>
       </c>
       <c r="E90">
-        <v>0.96428</v>
+        <v>0.9755900000000001</v>
       </c>
       <c r="F90">
-        <v>0.9952800000000001</v>
+        <v>1.00659</v>
       </c>
       <c r="G90">
         <v>0.054</v>
@@ -8661,37 +8661,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M90">
-        <v>0.234687024</v>
+        <v>0.237353922</v>
       </c>
       <c r="N90">
-        <v>-0.2160203573333334</v>
+        <v>-0.2186872553333334</v>
       </c>
       <c r="O90">
-        <v>-0.06264590362666667</v>
+        <v>-0.06341930404666667</v>
       </c>
       <c r="P90">
-        <v>-0.1533744537066667</v>
+        <v>-0.1552679512866667</v>
       </c>
       <c r="Q90">
-        <v>-0.1493744537066667</v>
+        <v>-0.1512679512866667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.049306867679062</v>
+        <v>1.140534764740795</v>
       </c>
       <c r="T90">
-        <v>6.137323081452315</v>
+        <v>6.695261543402526</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02306618082699507</v>
+        <v>0.02280701025590524</v>
       </c>
       <c r="W90">
-        <v>0.2303609945609946</v>
+        <v>0.2304221069816575</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.07953855457584502</v>
+        <v>0.07864486295139739</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3305344993351627</v>
+        <v>0.3324344993351627</v>
       </c>
       <c r="C91">
-        <v>-0.485290386784432</v>
+        <v>-0.4996979527339912</v>
       </c>
       <c r="D91">
-        <v>0.467299613215568</v>
+        <v>0.4642020472660088</v>
       </c>
       <c r="E91">
-        <v>0.9755900000000001</v>
+        <v>0.9869</v>
       </c>
       <c r="F91">
-        <v>1.00659</v>
+        <v>1.0179</v>
       </c>
       <c r="G91">
         <v>0.054</v>
@@ -8743,37 +8743,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M91">
-        <v>0.237353922</v>
+        <v>0.24002082</v>
       </c>
       <c r="N91">
-        <v>-0.2186872553333334</v>
+        <v>-0.2213541533333334</v>
       </c>
       <c r="O91">
-        <v>-0.06341930404666667</v>
+        <v>-0.06419270446666667</v>
       </c>
       <c r="P91">
-        <v>-0.1552679512866667</v>
+        <v>-0.1571614488666667</v>
       </c>
       <c r="Q91">
-        <v>-0.1512679512866667</v>
+        <v>-0.1531614488666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.140534764740795</v>
+        <v>1.250008241214875</v>
       </c>
       <c r="T91">
-        <v>6.695261543402526</v>
+        <v>7.364787697742779</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02280701025590524</v>
+        <v>0.02255359903083963</v>
       </c>
       <c r="W91">
-        <v>0.2304221069816575</v>
+        <v>0.230481861348528</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.07864486295139739</v>
+        <v>0.07777103114082629</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3324344993351627</v>
+        <v>0.3343344993351627</v>
       </c>
       <c r="C92">
-        <v>-0.4996979527339912</v>
+        <v>-0.5140647237330838</v>
       </c>
       <c r="D92">
-        <v>0.4642020472660088</v>
+        <v>0.4611452762669161</v>
       </c>
       <c r="E92">
-        <v>0.9869</v>
+        <v>0.9982099999999999</v>
       </c>
       <c r="F92">
-        <v>1.0179</v>
+        <v>1.02921</v>
       </c>
       <c r="G92">
         <v>0.054</v>
@@ -8825,37 +8825,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M92">
-        <v>0.24002082</v>
+        <v>0.242687718</v>
       </c>
       <c r="N92">
-        <v>-0.2213541533333334</v>
+        <v>-0.2240210513333333</v>
       </c>
       <c r="O92">
-        <v>-0.06419270446666667</v>
+        <v>-0.06496610488666667</v>
       </c>
       <c r="P92">
-        <v>-0.1571614488666667</v>
+        <v>-0.1590549464466667</v>
       </c>
       <c r="Q92">
-        <v>-0.1531614488666667</v>
+        <v>-0.1550549464466667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.250008241214875</v>
+        <v>1.383809156905416</v>
       </c>
       <c r="T92">
-        <v>7.364787697742779</v>
+        <v>8.183097441936422</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02255359903083963</v>
+        <v>0.02230575728324798</v>
       </c>
       <c r="W92">
-        <v>0.230481861348528</v>
+        <v>0.2305403024326101</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07777103114082629</v>
+        <v>0.07691640442499303</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3343344993351627</v>
+        <v>0.3362344993351627</v>
       </c>
       <c r="C93">
-        <v>-0.5140647237330838</v>
+        <v>-0.5283915004139288</v>
       </c>
       <c r="D93">
-        <v>0.4611452762669161</v>
+        <v>0.4581284995860713</v>
       </c>
       <c r="E93">
-        <v>0.9982099999999999</v>
+        <v>1.00952</v>
       </c>
       <c r="F93">
-        <v>1.02921</v>
+        <v>1.04052</v>
       </c>
       <c r="G93">
         <v>0.054</v>
@@ -8907,37 +8907,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M93">
-        <v>0.242687718</v>
+        <v>0.245354616</v>
       </c>
       <c r="N93">
-        <v>-0.2240210513333333</v>
+        <v>-0.2266879493333334</v>
       </c>
       <c r="O93">
-        <v>-0.06496610488666667</v>
+        <v>-0.06573950530666667</v>
       </c>
       <c r="P93">
-        <v>-0.1590549464466667</v>
+        <v>-0.1609484440266667</v>
       </c>
       <c r="Q93">
-        <v>-0.1550549464466667</v>
+        <v>-0.1569484440266667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.383809156905416</v>
+        <v>1.551060301518594</v>
       </c>
       <c r="T93">
-        <v>8.183097441936422</v>
+        <v>9.205984622178477</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02230575728324798</v>
+        <v>0.02206330339973442</v>
       </c>
       <c r="W93">
-        <v>0.2305403024326101</v>
+        <v>0.2305974730583426</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07691640442499303</v>
+        <v>0.07608035655080836</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3362344993351627</v>
+        <v>0.3381344993351627</v>
       </c>
       <c r="C94">
-        <v>-0.5283915004139288</v>
+        <v>-0.5426790625942157</v>
       </c>
       <c r="D94">
-        <v>0.4581284995860713</v>
+        <v>0.4551509374057843</v>
       </c>
       <c r="E94">
-        <v>1.00952</v>
+        <v>1.02083</v>
       </c>
       <c r="F94">
-        <v>1.04052</v>
+        <v>1.05183</v>
       </c>
       <c r="G94">
         <v>0.054</v>
@@ -8989,37 +8989,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M94">
-        <v>0.245354616</v>
+        <v>0.248021514</v>
       </c>
       <c r="N94">
-        <v>-0.2266879493333334</v>
+        <v>-0.2293548473333334</v>
       </c>
       <c r="O94">
-        <v>-0.06573950530666667</v>
+        <v>-0.06651290572666667</v>
       </c>
       <c r="P94">
-        <v>-0.1609484440266667</v>
+        <v>-0.1628419416066667</v>
       </c>
       <c r="Q94">
-        <v>-0.1569484440266667</v>
+        <v>-0.1588419416066667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.551060301518594</v>
+        <v>1.766097487449822</v>
       </c>
       <c r="T94">
-        <v>9.205984622178477</v>
+        <v>10.52112528248969</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02206330339973442</v>
+        <v>0.02182606357823189</v>
       </c>
       <c r="W94">
-        <v>0.2305974730583426</v>
+        <v>0.2306534142082529</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.07608035655080836</v>
+        <v>0.07526228820079961</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3381344993351627</v>
+        <v>0.3400344993351627</v>
       </c>
       <c r="C95">
-        <v>-0.5426790625942157</v>
+        <v>-0.5569281699491485</v>
       </c>
       <c r="D95">
-        <v>0.4551509374057843</v>
+        <v>0.4522118300508514</v>
       </c>
       <c r="E95">
-        <v>1.02083</v>
+        <v>1.03214</v>
       </c>
       <c r="F95">
-        <v>1.05183</v>
+        <v>1.06314</v>
       </c>
       <c r="G95">
         <v>0.054</v>
@@ -9071,37 +9071,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M95">
-        <v>0.248021514</v>
+        <v>0.250688412</v>
       </c>
       <c r="N95">
-        <v>-0.2293548473333334</v>
+        <v>-0.2320217453333334</v>
       </c>
       <c r="O95">
-        <v>-0.06651290572666667</v>
+        <v>-0.06728630614666667</v>
       </c>
       <c r="P95">
-        <v>-0.1628419416066667</v>
+        <v>-0.1647354391866667</v>
       </c>
       <c r="Q95">
-        <v>-0.1588419416066667</v>
+        <v>-0.1607354391866667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.766097487449822</v>
+        <v>2.052813735358126</v>
       </c>
       <c r="T95">
-        <v>10.52112528248969</v>
+        <v>12.27464616290464</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02182606357823189</v>
+        <v>0.02159387141250602</v>
       </c>
       <c r="W95">
-        <v>0.2306534142082529</v>
+        <v>0.2307081651209311</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07526228820079961</v>
+        <v>0.07446162556036562</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3400344993351627</v>
+        <v>0.3419344993351627</v>
       </c>
       <c r="C96">
-        <v>-0.5569281699491485</v>
+        <v>-0.5711395626576159</v>
       </c>
       <c r="D96">
-        <v>0.4522118300508514</v>
+        <v>0.4493104373423842</v>
       </c>
       <c r="E96">
-        <v>1.03214</v>
+        <v>1.04345</v>
       </c>
       <c r="F96">
-        <v>1.06314</v>
+        <v>1.07445</v>
       </c>
       <c r="G96">
         <v>0.054</v>
@@ -9153,37 +9153,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M96">
-        <v>0.250688412</v>
+        <v>0.2533553100000001</v>
       </c>
       <c r="N96">
-        <v>-0.2320217453333334</v>
+        <v>-0.2346886433333334</v>
       </c>
       <c r="O96">
-        <v>-0.06728630614666667</v>
+        <v>-0.06805970656666668</v>
       </c>
       <c r="P96">
-        <v>-0.1647354391866667</v>
+        <v>-0.1666289367666667</v>
       </c>
       <c r="Q96">
-        <v>-0.1607354391866667</v>
+        <v>-0.1626289367666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.052813735358126</v>
+        <v>2.454216482429752</v>
       </c>
       <c r="T96">
-        <v>12.27464616290464</v>
+        <v>14.72957539548558</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02159387141250602</v>
+        <v>0.0213665675029007</v>
       </c>
       <c r="W96">
-        <v>0.2307081651209311</v>
+        <v>0.230761763382816</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07446162556036562</v>
+        <v>0.07367781897551962</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3419344993351627</v>
+        <v>0.3438344993351626</v>
       </c>
       <c r="C97">
-        <v>-0.5711395626576159</v>
+        <v>-0.5853139620236452</v>
       </c>
       <c r="D97">
-        <v>0.4493104373423842</v>
+        <v>0.4464460379763549</v>
       </c>
       <c r="E97">
-        <v>1.04345</v>
+        <v>1.05476</v>
       </c>
       <c r="F97">
-        <v>1.07445</v>
+        <v>1.08576</v>
       </c>
       <c r="G97">
         <v>0.054</v>
@@ -9235,37 +9235,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M97">
-        <v>0.2533553100000001</v>
+        <v>0.256022208</v>
       </c>
       <c r="N97">
-        <v>-0.2346886433333334</v>
+        <v>-0.2373555413333334</v>
       </c>
       <c r="O97">
-        <v>-0.06805970656666668</v>
+        <v>-0.06883310698666667</v>
       </c>
       <c r="P97">
-        <v>-0.1666289367666667</v>
+        <v>-0.1685224343466667</v>
       </c>
       <c r="Q97">
-        <v>-0.1626289367666667</v>
+        <v>-0.1645224343466667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.454216482429752</v>
+        <v>3.056320603037191</v>
       </c>
       <c r="T97">
-        <v>14.72957539548558</v>
+        <v>18.41196924435698</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0213665675029007</v>
+        <v>0.02114399909141215</v>
       </c>
       <c r="W97">
-        <v>0.230761763382816</v>
+        <v>0.230814245014245</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07367781897551962</v>
+        <v>0.07291034169452471</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3438344993351626</v>
+        <v>0.3457344993351626</v>
       </c>
       <c r="C98">
-        <v>-0.5853139620236452</v>
+        <v>-0.5994520710742388</v>
       </c>
       <c r="D98">
-        <v>0.4464460379763549</v>
+        <v>0.4436179289257611</v>
       </c>
       <c r="E98">
-        <v>1.05476</v>
+        <v>1.06607</v>
       </c>
       <c r="F98">
-        <v>1.08576</v>
+        <v>1.09707</v>
       </c>
       <c r="G98">
         <v>0.054</v>
@@ -9317,37 +9317,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M98">
-        <v>0.256022208</v>
+        <v>0.258689106</v>
       </c>
       <c r="N98">
-        <v>-0.2373555413333334</v>
+        <v>-0.2400224393333333</v>
       </c>
       <c r="O98">
-        <v>-0.06883310698666667</v>
+        <v>-0.06960650740666666</v>
       </c>
       <c r="P98">
-        <v>-0.1685224343466667</v>
+        <v>-0.1704159319266667</v>
       </c>
       <c r="Q98">
-        <v>-0.1645224343466667</v>
+        <v>-0.1664159319266667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.056320603037183</v>
+        <v>4.059827470716245</v>
       </c>
       <c r="T98">
-        <v>18.41196924435693</v>
+        <v>24.54929232580924</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02114399909141215</v>
+        <v>0.02092601971933573</v>
       </c>
       <c r="W98">
-        <v>0.230814245014245</v>
+        <v>0.2308656445501807</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07291034169452471</v>
+        <v>0.07215868868736464</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3457344993351626</v>
+        <v>0.3476344993351627</v>
       </c>
       <c r="C99">
-        <v>-0.5994520710742388</v>
+        <v>-0.6135545751346279</v>
       </c>
       <c r="D99">
-        <v>0.4436179289257611</v>
+        <v>0.440825424865372</v>
       </c>
       <c r="E99">
-        <v>1.06607</v>
+        <v>1.07738</v>
       </c>
       <c r="F99">
-        <v>1.09707</v>
+        <v>1.10838</v>
       </c>
       <c r="G99">
         <v>0.054</v>
@@ -9399,37 +9399,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M99">
-        <v>0.258689106</v>
+        <v>0.261356004</v>
       </c>
       <c r="N99">
-        <v>-0.2400224393333333</v>
+        <v>-0.2426893373333333</v>
       </c>
       <c r="O99">
-        <v>-0.06960650740666666</v>
+        <v>-0.07037990782666666</v>
       </c>
       <c r="P99">
-        <v>-0.1704159319266667</v>
+        <v>-0.1723094295066667</v>
       </c>
       <c r="Q99">
-        <v>-0.1664159319266667</v>
+        <v>-0.1683094295066667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.059827470716245</v>
+        <v>6.066841206074367</v>
       </c>
       <c r="T99">
-        <v>24.54929232580924</v>
+        <v>36.82393848871386</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02092601971933573</v>
+        <v>0.02071248890587313</v>
       </c>
       <c r="W99">
-        <v>0.2308656445501807</v>
+        <v>0.2309159951159951</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07215868868736464</v>
+        <v>0.07142237553749353</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3476344993351627</v>
+        <v>0.3495344993351627</v>
       </c>
       <c r="C100">
-        <v>-0.6135545751346279</v>
+        <v>-0.6276221423819364</v>
       </c>
       <c r="D100">
-        <v>0.440825424865372</v>
+        <v>0.4380678576180638</v>
       </c>
       <c r="E100">
-        <v>1.07738</v>
+        <v>1.08869</v>
       </c>
       <c r="F100">
-        <v>1.10838</v>
+        <v>1.11969</v>
       </c>
       <c r="G100">
         <v>0.054</v>
@@ -9481,37 +9481,37 @@
         <v>0.01866666666666666</v>
       </c>
       <c r="M100">
-        <v>0.261356004</v>
+        <v>0.264022902</v>
       </c>
       <c r="N100">
-        <v>-0.2426893373333333</v>
+        <v>-0.2453562353333333</v>
       </c>
       <c r="O100">
-        <v>-0.07037990782666666</v>
+        <v>-0.07115330824666666</v>
       </c>
       <c r="P100">
-        <v>-0.1723094295066667</v>
+        <v>-0.1742029270866667</v>
       </c>
       <c r="Q100">
-        <v>-0.1683094295066667</v>
+        <v>-0.1702029270866667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.066841206074367</v>
+        <v>12.08788241214873</v>
       </c>
       <c r="T100">
-        <v>36.82393848871386</v>
+        <v>73.64787697742771</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02071248890587313</v>
+        <v>0.02050327184621784</v>
       </c>
       <c r="W100">
-        <v>0.2309159951159951</v>
+        <v>0.2309653284986619</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07142237553749353</v>
+        <v>0.07070093740075123</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3495344993351627</v>
-      </c>
-      <c r="C101">
-        <v>-0.6276221423819364</v>
-      </c>
-      <c r="D101">
-        <v>0.4380678576180638</v>
-      </c>
-      <c r="E101">
-        <v>1.08869</v>
-      </c>
-      <c r="F101">
-        <v>1.11969</v>
-      </c>
-      <c r="G101">
-        <v>0.054</v>
-      </c>
-      <c r="H101">
-        <v>1.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.02266666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.004000000000000002</v>
-      </c>
-      <c r="L101">
-        <v>0.01866666666666666</v>
-      </c>
-      <c r="M101">
-        <v>0.264022902</v>
-      </c>
-      <c r="N101">
-        <v>-0.2453562353333333</v>
-      </c>
-      <c r="O101">
-        <v>-0.07115330824666666</v>
-      </c>
-      <c r="P101">
-        <v>-0.1742029270866667</v>
-      </c>
-      <c r="Q101">
-        <v>-0.1702029270866667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.08788241214873</v>
-      </c>
-      <c r="T101">
-        <v>73.64787697742771</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02050327184621784</v>
-      </c>
-      <c r="W101">
-        <v>0.2309653284986619</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07070093740075123</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
